--- a/artfynd/A 33533-2025 artfynd.xlsx
+++ b/artfynd/A 33533-2025 artfynd.xlsx
@@ -5136,10 +5136,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127442782</v>
+        <v>127444496</v>
       </c>
       <c r="B43" t="n">
-        <v>57657</v>
+        <v>75138</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5147,39 +5147,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>478059</v>
+        <v>478229</v>
       </c>
       <c r="R43" t="n">
-        <v>6820910</v>
+        <v>6821051</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5248,10 +5243,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127444496</v>
+        <v>127444690</v>
       </c>
       <c r="B44" t="n">
-        <v>75138</v>
+        <v>57817</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5259,37 +5254,42 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6440</v>
+        <v>103021</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Harabacken, Dlr</t>
+          <t>Harabacken, Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>478229</v>
+        <v>478062</v>
       </c>
       <c r="R44" t="n">
-        <v>6821051</v>
+        <v>6821226</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5318,7 +5318,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5328,7 +5328,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5343,22 +5343,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127444690</v>
+        <v>127443816</v>
       </c>
       <c r="B45" t="n">
-        <v>57817</v>
+        <v>79046</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5366,42 +5366,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>103021</v>
+        <v>185</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Harabacken, Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>478062</v>
+        <v>478071</v>
       </c>
       <c r="R45" t="n">
-        <v>6821226</v>
+        <v>6821147</v>
       </c>
       <c r="S45" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5430,7 +5425,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5440,7 +5435,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5467,48 +5462,53 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127443816</v>
+        <v>127443685</v>
       </c>
       <c r="B46" t="n">
-        <v>79046</v>
+        <v>58027</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>185</v>
+        <v>103015</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Harabacken, Harabacken, Dlr</t>
+          <t>Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>478071</v>
+        <v>478128</v>
       </c>
       <c r="R46" t="n">
-        <v>6821147</v>
+        <v>6820965</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5537,7 +5537,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5547,7 +5547,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5562,65 +5562,60 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127443685</v>
+        <v>127444469</v>
       </c>
       <c r="B47" t="n">
-        <v>58027</v>
+        <v>79014</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Harabacken, Dlr</t>
+          <t>Harabacken, Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>478128</v>
+        <v>478048</v>
       </c>
       <c r="R47" t="n">
-        <v>6820965</v>
+        <v>6821183</v>
       </c>
       <c r="S47" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5649,7 +5644,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5659,7 +5654,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5674,22 +5669,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127443715</v>
+        <v>127445040</v>
       </c>
       <c r="B48" t="n">
-        <v>79046</v>
+        <v>79014</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5697,37 +5692,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Kuusikallio, Kuusikallio, Dlr</t>
+          <t>Harabacken, Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>478069</v>
+        <v>478072</v>
       </c>
       <c r="R48" t="n">
-        <v>6821132</v>
+        <v>6821204</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5756,7 +5751,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5766,7 +5761,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5781,22 +5781,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127444469</v>
+        <v>127443715</v>
       </c>
       <c r="B49" t="n">
-        <v>79014</v>
+        <v>79046</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5804,34 +5804,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Harabacken, Harabacken, Dlr</t>
+          <t>Kuusikallio, Kuusikallio, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>478048</v>
+        <v>478069</v>
       </c>
       <c r="R49" t="n">
-        <v>6821183</v>
+        <v>6821132</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5863,7 +5863,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5873,7 +5873,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5900,7 +5900,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127445040</v>
+        <v>127443980</v>
       </c>
       <c r="B50" t="n">
         <v>79014</v>
@@ -5931,17 +5931,17 @@
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Harabacken, Harabacken, Dlr</t>
+          <t>Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>478072</v>
+        <v>478207</v>
       </c>
       <c r="R50" t="n">
-        <v>6821204</v>
+        <v>6821016</v>
       </c>
       <c r="S50" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5970,7 +5970,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5980,12 +5980,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:22</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>På tall</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6000,22 +5995,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127443980</v>
+        <v>127444902</v>
       </c>
       <c r="B51" t="n">
-        <v>79014</v>
+        <v>79046</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6023,37 +6018,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Harabacken, Dlr</t>
+          <t>Harabacken, Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>478207</v>
+        <v>478072</v>
       </c>
       <c r="R51" t="n">
-        <v>6821016</v>
+        <v>6821204</v>
       </c>
       <c r="S51" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6082,7 +6077,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6092,7 +6087,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6107,22 +6107,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127444902</v>
+        <v>127442782</v>
       </c>
       <c r="B52" t="n">
-        <v>79046</v>
+        <v>57657</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6130,37 +6130,45 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Harabacken, Harabacken, Dlr</t>
+          <t>Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>478072</v>
+        <v>478059</v>
       </c>
       <c r="R52" t="n">
-        <v>6821204</v>
+        <v>6820910</v>
       </c>
       <c r="S52" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6189,7 +6197,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6199,12 +6207,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:22</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>På gran</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6219,12 +6222,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>

--- a/artfynd/A 33533-2025 artfynd.xlsx
+++ b/artfynd/A 33533-2025 artfynd.xlsx
@@ -1113,7 +1113,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127442809</v>
+        <v>127445814</v>
       </c>
       <c r="B6" t="n">
         <v>79014</v>
@@ -1144,17 +1144,17 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kuusikallio, Kuusikallio, Dlr</t>
+          <t>Harabacken, Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>478309</v>
+        <v>478096</v>
       </c>
       <c r="R6" t="n">
-        <v>6820751</v>
+        <v>6821144</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1220,10 +1220,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127445814</v>
+        <v>127445695</v>
       </c>
       <c r="B7" t="n">
-        <v>79014</v>
+        <v>57654</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1231,34 +1231,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Harabacken, Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>478096</v>
+        <v>478104</v>
       </c>
       <c r="R7" t="n">
-        <v>6821144</v>
+        <v>6821165</v>
       </c>
       <c r="S7" t="n">
         <v>9</v>
@@ -1327,10 +1332,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127445695</v>
+        <v>127444509</v>
       </c>
       <c r="B8" t="n">
-        <v>57654</v>
+        <v>79014</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1338,42 +1343,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Harabacken, Harabacken, Dlr</t>
+          <t>Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>478104</v>
+        <v>478229</v>
       </c>
       <c r="R8" t="n">
-        <v>6821165</v>
+        <v>6821051</v>
       </c>
       <c r="S8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1402,7 +1402,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1412,7 +1412,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1427,19 +1427,19 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127444509</v>
+        <v>127442809</v>
       </c>
       <c r="B9" t="n">
         <v>79014</v>
@@ -1470,17 +1470,17 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Harabacken, Dlr</t>
+          <t>Kuusikallio, Kuusikallio, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>478229</v>
+        <v>478309</v>
       </c>
       <c r="R9" t="n">
-        <v>6821051</v>
+        <v>6820751</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1519,7 +1519,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1534,12 +1534,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -3390,10 +3390,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127451855</v>
+        <v>127445678</v>
       </c>
       <c r="B27" t="n">
-        <v>79046</v>
+        <v>57657</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3401,40 +3401,42 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Harabacken, Dlr</t>
+          <t>Kuusikallio, Kuusikallio, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>478077</v>
+        <v>478106</v>
       </c>
       <c r="R27" t="n">
-        <v>6820974</v>
+        <v>6821168</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3461,14 +3463,19 @@
           <t>2025-08-13</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-08-13</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>På gran</t>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3477,29 +3484,28 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127445678</v>
+        <v>127445612</v>
       </c>
       <c r="B28" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3507,42 +3513,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Kuusikallio, Kuusikallio, Dlr</t>
+          <t>Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>478106</v>
+        <v>478265</v>
       </c>
       <c r="R28" t="n">
-        <v>6821168</v>
+        <v>6821033</v>
       </c>
       <c r="S28" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3571,7 +3572,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3581,7 +3582,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3596,22 +3597,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127445612</v>
+        <v>127451855</v>
       </c>
       <c r="B29" t="n">
-        <v>79014</v>
+        <v>79046</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3619,37 +3620,40 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>478265</v>
+        <v>478077</v>
       </c>
       <c r="R29" t="n">
-        <v>6821033</v>
+        <v>6820974</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3676,19 +3680,14 @@
           <t>2025-08-13</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>10:20</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-08-13</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>10:20</t>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3697,18 +3696,19 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -5574,10 +5574,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127444469</v>
+        <v>127443715</v>
       </c>
       <c r="B47" t="n">
-        <v>79014</v>
+        <v>79046</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5585,34 +5585,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Harabacken, Harabacken, Dlr</t>
+          <t>Kuusikallio, Kuusikallio, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>478048</v>
+        <v>478069</v>
       </c>
       <c r="R47" t="n">
-        <v>6821183</v>
+        <v>6821132</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5644,7 +5644,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5654,7 +5654,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5681,7 +5681,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127445040</v>
+        <v>127444469</v>
       </c>
       <c r="B48" t="n">
         <v>79014</v>
@@ -5716,13 +5716,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>478072</v>
+        <v>478048</v>
       </c>
       <c r="R48" t="n">
-        <v>6821204</v>
+        <v>6821183</v>
       </c>
       <c r="S48" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5761,12 +5761,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:22</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>På tall</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5781,22 +5776,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127443715</v>
+        <v>127445040</v>
       </c>
       <c r="B49" t="n">
-        <v>79046</v>
+        <v>79014</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5804,37 +5799,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Kuusikallio, Kuusikallio, Dlr</t>
+          <t>Harabacken, Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>478069</v>
+        <v>478072</v>
       </c>
       <c r="R49" t="n">
-        <v>6821132</v>
+        <v>6821204</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5863,7 +5858,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5873,7 +5868,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5888,12 +5888,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>

--- a/artfynd/A 33533-2025 artfynd.xlsx
+++ b/artfynd/A 33533-2025 artfynd.xlsx
@@ -675,48 +675,53 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127443978</v>
+        <v>127444794</v>
       </c>
       <c r="B2" t="n">
-        <v>75138</v>
+        <v>5177</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6440</v>
+        <v>100526</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Harabacken, Dlr</t>
+          <t>Harabacken, Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>478207</v>
+        <v>478062</v>
       </c>
       <c r="R2" t="n">
-        <v>6821016</v>
+        <v>6821226</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,12 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:20</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Vitgrynig nållav på äldre gran</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,12 +775,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -790,7 +790,7 @@
         <v>127445512</v>
       </c>
       <c r="B3" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -894,53 +894,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127444794</v>
+        <v>127443978</v>
       </c>
       <c r="B4" t="n">
-        <v>5176</v>
+        <v>75142</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100526</v>
+        <v>6440</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Harabacken, Harabacken, Dlr</t>
+          <t>Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>478062</v>
+        <v>478207</v>
       </c>
       <c r="R4" t="n">
-        <v>6821226</v>
+        <v>6821016</v>
       </c>
       <c r="S4" t="n">
-        <v>9</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -969,7 +964,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -979,7 +974,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav på äldre gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -994,12 +994,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1009,7 +1009,7 @@
         <v>127445652</v>
       </c>
       <c r="B5" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127445814</v>
+        <v>127442809</v>
       </c>
       <c r="B6" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1144,17 +1144,17 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Harabacken, Harabacken, Dlr</t>
+          <t>Kuusikallio, Kuusikallio, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>478096</v>
+        <v>478309</v>
       </c>
       <c r="R6" t="n">
-        <v>6821144</v>
+        <v>6820751</v>
       </c>
       <c r="S6" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1220,10 +1220,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127445695</v>
+        <v>127445814</v>
       </c>
       <c r="B7" t="n">
-        <v>57654</v>
+        <v>79018</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1231,39 +1231,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Harabacken, Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>478104</v>
+        <v>478096</v>
       </c>
       <c r="R7" t="n">
-        <v>6821165</v>
+        <v>6821144</v>
       </c>
       <c r="S7" t="n">
         <v>9</v>
@@ -1335,7 +1330,7 @@
         <v>127444509</v>
       </c>
       <c r="B8" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1439,10 +1434,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127442809</v>
+        <v>127445695</v>
       </c>
       <c r="B9" t="n">
-        <v>79014</v>
+        <v>57658</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1450,37 +1445,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kuusikallio, Kuusikallio, Dlr</t>
+          <t>Harabacken, Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>478309</v>
+        <v>478104</v>
       </c>
       <c r="R9" t="n">
-        <v>6820751</v>
+        <v>6821165</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1519,7 +1519,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1546,10 +1546,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127447989</v>
+        <v>127444616</v>
       </c>
       <c r="B10" t="n">
-        <v>79014</v>
+        <v>79050</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1557,34 +1557,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Harabacken, Dlr</t>
+          <t>Harabacken, Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>478360</v>
+        <v>478034</v>
       </c>
       <c r="R10" t="n">
-        <v>6820946</v>
+        <v>6821199</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1616,7 +1616,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1641,22 +1641,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127442751</v>
+        <v>127447989</v>
       </c>
       <c r="B11" t="n">
-        <v>57654</v>
+        <v>79018</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1664,39 +1664,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>478022</v>
+        <v>478360</v>
       </c>
       <c r="R11" t="n">
-        <v>6820902</v>
+        <v>6820946</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1765,10 +1760,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127444616</v>
+        <v>127442751</v>
       </c>
       <c r="B12" t="n">
-        <v>79046</v>
+        <v>57658</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1776,34 +1771,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>185</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Harabacken, Harabacken, Dlr</t>
+          <t>Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>478034</v>
+        <v>478022</v>
       </c>
       <c r="R12" t="n">
-        <v>6821199</v>
+        <v>6820902</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1860,44 +1860,44 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127443080</v>
+        <v>127444817</v>
       </c>
       <c r="B13" t="n">
-        <v>98360</v>
+        <v>79050</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219790</v>
+        <v>185</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1907,13 +1907,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>478309</v>
+        <v>478071</v>
       </c>
       <c r="R13" t="n">
-        <v>6820751</v>
+        <v>6821227</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1952,7 +1952,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1967,44 +1972,44 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127444817</v>
+        <v>127443080</v>
       </c>
       <c r="B14" t="n">
-        <v>79046</v>
+        <v>98364</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>185</v>
+        <v>219790</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2014,13 +2019,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>478071</v>
+        <v>478309</v>
       </c>
       <c r="R14" t="n">
-        <v>6821227</v>
+        <v>6820751</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2049,7 +2054,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2059,12 +2064,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:22</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>På gran</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2079,12 +2079,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2094,7 +2094,7 @@
         <v>127444484</v>
       </c>
       <c r="B15" t="n">
-        <v>79046</v>
+        <v>79050</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2198,10 +2198,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127444510</v>
+        <v>127444563</v>
       </c>
       <c r="B16" t="n">
-        <v>57657</v>
+        <v>79050</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2209,39 +2209,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Harabacken, Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>478030</v>
+        <v>478024</v>
       </c>
       <c r="R16" t="n">
-        <v>6821195</v>
+        <v>6821213</v>
       </c>
       <c r="S16" t="n">
         <v>9</v>
@@ -2273,7 +2268,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2283,7 +2278,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2298,22 +2293,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
+          <t>Bo karlstens, Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127444563</v>
+        <v>127444510</v>
       </c>
       <c r="B17" t="n">
-        <v>79046</v>
+        <v>57661</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2321,34 +2316,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Harabacken, Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>478024</v>
+        <v>478030</v>
       </c>
       <c r="R17" t="n">
-        <v>6821213</v>
+        <v>6821195</v>
       </c>
       <c r="S17" t="n">
         <v>9</v>
@@ -2380,7 +2380,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2390,7 +2390,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2405,12 +2405,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Bo karlstens, Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2420,7 +2420,7 @@
         <v>127443766</v>
       </c>
       <c r="B18" t="n">
-        <v>5176</v>
+        <v>5177</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
         <v>127442676</v>
       </c>
       <c r="B19" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2634,7 +2634,7 @@
         <v>127444686</v>
       </c>
       <c r="B20" t="n">
-        <v>79046</v>
+        <v>79050</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2741,7 +2741,7 @@
         <v>127444556</v>
       </c>
       <c r="B21" t="n">
-        <v>79046</v>
+        <v>79050</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2845,10 +2845,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127443690</v>
+        <v>127443809</v>
       </c>
       <c r="B22" t="n">
-        <v>57654</v>
+        <v>79050</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2856,42 +2856,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>185</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Harabacken, Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>478071</v>
+        <v>478054</v>
       </c>
       <c r="R22" t="n">
-        <v>6821124</v>
+        <v>6821168</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2920,7 +2915,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2930,7 +2925,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2945,22 +2940,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127443809</v>
+        <v>127444809</v>
       </c>
       <c r="B23" t="n">
-        <v>79046</v>
+        <v>79018</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2968,21 +2963,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2992,13 +2987,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>478054</v>
+        <v>478062</v>
       </c>
       <c r="R23" t="n">
-        <v>6821168</v>
+        <v>6821226</v>
       </c>
       <c r="S23" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3027,7 +3022,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3037,7 +3032,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3052,12 +3047,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bo karlstens, Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -3067,7 +3062,7 @@
         <v>127443315</v>
       </c>
       <c r="B24" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3171,10 +3166,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127444809</v>
+        <v>127443690</v>
       </c>
       <c r="B25" t="n">
-        <v>79014</v>
+        <v>57658</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3182,37 +3177,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Harabacken, Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>478062</v>
+        <v>478071</v>
       </c>
       <c r="R25" t="n">
-        <v>6821226</v>
+        <v>6821124</v>
       </c>
       <c r="S25" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3266,12 +3266,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Bo karlstens, Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3281,7 +3281,7 @@
         <v>127444600</v>
       </c>
       <c r="B26" t="n">
-        <v>57654</v>
+        <v>57658</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3390,10 +3390,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127445678</v>
+        <v>127445612</v>
       </c>
       <c r="B27" t="n">
-        <v>57657</v>
+        <v>79018</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3401,42 +3401,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Kuusikallio, Kuusikallio, Dlr</t>
+          <t>Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>478106</v>
+        <v>478265</v>
       </c>
       <c r="R27" t="n">
-        <v>6821168</v>
+        <v>6821033</v>
       </c>
       <c r="S27" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3465,7 +3460,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3475,7 +3470,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3490,22 +3485,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127445612</v>
+        <v>127445678</v>
       </c>
       <c r="B28" t="n">
-        <v>79014</v>
+        <v>57661</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3513,37 +3508,42 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Harabacken, Dlr</t>
+          <t>Kuusikallio, Kuusikallio, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>478265</v>
+        <v>478106</v>
       </c>
       <c r="R28" t="n">
-        <v>6821033</v>
+        <v>6821168</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3572,7 +3572,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3582,7 +3582,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3597,12 +3597,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -3612,7 +3612,7 @@
         <v>127451855</v>
       </c>
       <c r="B29" t="n">
-        <v>79046</v>
+        <v>79050</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3715,10 +3715,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127441057</v>
+        <v>127443983</v>
       </c>
       <c r="B30" t="n">
-        <v>57654</v>
+        <v>91330</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3726,42 +3726,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Harabacken, Dlr</t>
+          <t>Kuusikallio, Kuusikallio, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>478319</v>
+        <v>478068</v>
       </c>
       <c r="R30" t="n">
-        <v>6820790</v>
+        <v>6821169</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3790,7 +3785,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3800,7 +3795,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3815,22 +3810,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127443983</v>
+        <v>127445756</v>
       </c>
       <c r="B31" t="n">
-        <v>91326</v>
+        <v>79018</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3838,37 +3833,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Kuusikallio, Kuusikallio, Dlr</t>
+          <t>Harabacken, Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>478068</v>
+        <v>478104</v>
       </c>
       <c r="R31" t="n">
-        <v>6821169</v>
+        <v>6821165</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3897,7 +3892,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3907,7 +3902,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3934,10 +3929,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127445756</v>
+        <v>127441057</v>
       </c>
       <c r="B32" t="n">
-        <v>79014</v>
+        <v>57658</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3945,37 +3940,42 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Harabacken, Harabacken, Dlr</t>
+          <t>Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>478104</v>
+        <v>478319</v>
       </c>
       <c r="R32" t="n">
-        <v>6821165</v>
+        <v>6820790</v>
       </c>
       <c r="S32" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4004,7 +4004,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4014,7 +4014,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4029,22 +4029,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127444374</v>
+        <v>127444793</v>
       </c>
       <c r="B33" t="n">
-        <v>79046</v>
+        <v>57821</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4052,34 +4052,39 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>185</v>
+        <v>103021</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Harabacken, Harabacken, Dlr</t>
+          <t>Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>478068</v>
+        <v>478245</v>
       </c>
       <c r="R33" t="n">
-        <v>6821169</v>
+        <v>6821068</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4111,7 +4116,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4121,7 +4126,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4136,12 +4141,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4151,7 +4156,7 @@
         <v>127444491</v>
       </c>
       <c r="B34" t="n">
-        <v>79046</v>
+        <v>79050</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4260,10 +4265,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127444793</v>
+        <v>127444374</v>
       </c>
       <c r="B35" t="n">
-        <v>57817</v>
+        <v>79050</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4271,39 +4276,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103021</v>
+        <v>185</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Harabacken, Dlr</t>
+          <t>Harabacken, Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>478245</v>
+        <v>478068</v>
       </c>
       <c r="R35" t="n">
-        <v>6821068</v>
+        <v>6821169</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4335,7 +4335,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4345,7 +4345,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4360,12 +4360,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -4375,7 +4375,7 @@
         <v>127444001</v>
       </c>
       <c r="B36" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4482,7 +4482,7 @@
         <v>127443762</v>
       </c>
       <c r="B37" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4591,10 +4591,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127445635</v>
+        <v>127444502</v>
       </c>
       <c r="B38" t="n">
-        <v>79603</v>
+        <v>57661</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4602,37 +4602,42 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Harabacken, Dlr</t>
+          <t>Harabacken, Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>478265</v>
+        <v>478062</v>
       </c>
       <c r="R38" t="n">
-        <v>6821019</v>
+        <v>6821201</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4661,7 +4666,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4671,7 +4676,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4686,22 +4691,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127444502</v>
+        <v>127445635</v>
       </c>
       <c r="B39" t="n">
-        <v>57657</v>
+        <v>79607</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4709,42 +4714,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Harabacken, Harabacken, Dlr</t>
+          <t>Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>478062</v>
+        <v>478265</v>
       </c>
       <c r="R39" t="n">
-        <v>6821201</v>
+        <v>6821019</v>
       </c>
       <c r="S39" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4773,7 +4773,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4783,7 +4783,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4798,12 +4798,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -4813,7 +4813,7 @@
         <v>127443785</v>
       </c>
       <c r="B40" t="n">
-        <v>58027</v>
+        <v>58031</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4925,7 +4925,7 @@
         <v>127444767</v>
       </c>
       <c r="B41" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5032,7 +5032,7 @@
         <v>127443466</v>
       </c>
       <c r="B42" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5139,7 +5139,7 @@
         <v>127444496</v>
       </c>
       <c r="B43" t="n">
-        <v>75138</v>
+        <v>75142</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5246,7 +5246,7 @@
         <v>127444690</v>
       </c>
       <c r="B44" t="n">
-        <v>57817</v>
+        <v>57821</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5355,48 +5355,53 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127443816</v>
+        <v>127443685</v>
       </c>
       <c r="B45" t="n">
-        <v>79046</v>
+        <v>58031</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>185</v>
+        <v>103015</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Harabacken, Harabacken, Dlr</t>
+          <t>Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>478071</v>
+        <v>478128</v>
       </c>
       <c r="R45" t="n">
-        <v>6821147</v>
+        <v>6820965</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5425,7 +5430,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5435,7 +5440,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5450,65 +5455,60 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127443685</v>
+        <v>127443816</v>
       </c>
       <c r="B46" t="n">
-        <v>58027</v>
+        <v>79050</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>103015</v>
+        <v>185</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Harabacken, Dlr</t>
+          <t>Harabacken, Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>478128</v>
+        <v>478071</v>
       </c>
       <c r="R46" t="n">
-        <v>6820965</v>
+        <v>6821147</v>
       </c>
       <c r="S46" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5537,7 +5537,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5547,7 +5547,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5562,12 +5562,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -5577,7 +5577,7 @@
         <v>127443715</v>
       </c>
       <c r="B47" t="n">
-        <v>79046</v>
+        <v>79050</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5684,7 +5684,7 @@
         <v>127444469</v>
       </c>
       <c r="B48" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5791,7 +5791,7 @@
         <v>127445040</v>
       </c>
       <c r="B49" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5900,10 +5900,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127443980</v>
+        <v>127444902</v>
       </c>
       <c r="B50" t="n">
-        <v>79014</v>
+        <v>79050</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5911,37 +5911,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Harabacken, Dlr</t>
+          <t>Harabacken, Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>478207</v>
+        <v>478072</v>
       </c>
       <c r="R50" t="n">
-        <v>6821016</v>
+        <v>6821204</v>
       </c>
       <c r="S50" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5970,7 +5970,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5980,7 +5980,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5995,22 +6000,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127444902</v>
+        <v>127443980</v>
       </c>
       <c r="B51" t="n">
-        <v>79046</v>
+        <v>79018</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6018,37 +6023,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Harabacken, Harabacken, Dlr</t>
+          <t>Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>478072</v>
+        <v>478207</v>
       </c>
       <c r="R51" t="n">
-        <v>6821204</v>
+        <v>6821016</v>
       </c>
       <c r="S51" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6077,7 +6082,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6087,12 +6092,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:22</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>På gran</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6107,12 +6107,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
@@ -6122,7 +6122,7 @@
         <v>127442782</v>
       </c>
       <c r="B52" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>

--- a/artfynd/A 33533-2025 artfynd.xlsx
+++ b/artfynd/A 33533-2025 artfynd.xlsx
@@ -675,53 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127444794</v>
+        <v>127443978</v>
       </c>
       <c r="B2" t="n">
-        <v>5177</v>
+        <v>75142</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100526</v>
+        <v>6440</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Harabacken, Harabacken, Dlr</t>
+          <t>Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>478062</v>
+        <v>478207</v>
       </c>
       <c r="R2" t="n">
-        <v>6821226</v>
+        <v>6821016</v>
       </c>
       <c r="S2" t="n">
-        <v>9</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +755,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav på äldre gran</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,12 +775,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -894,10 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127443978</v>
+        <v>127445652</v>
       </c>
       <c r="B4" t="n">
-        <v>75142</v>
+        <v>79018</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -905,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,13 +929,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>478207</v>
+        <v>478270</v>
       </c>
       <c r="R4" t="n">
-        <v>6821016</v>
+        <v>6821004</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -975,11 +975,6 @@
       <c r="AB4" t="inlineStr">
         <is>
           <t>10:20</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Vitgrynig nållav på äldre gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1006,48 +1001,53 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127445652</v>
+        <v>127444794</v>
       </c>
       <c r="B5" t="n">
-        <v>79018</v>
+        <v>5177</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Harabacken, Dlr</t>
+          <t>Harabacken, Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>478270</v>
+        <v>478062</v>
       </c>
       <c r="R5" t="n">
-        <v>6821004</v>
+        <v>6821226</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1101,22 +1101,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127442809</v>
+        <v>127445695</v>
       </c>
       <c r="B6" t="n">
-        <v>79018</v>
+        <v>57658</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1124,37 +1124,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kuusikallio, Kuusikallio, Dlr</t>
+          <t>Harabacken, Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>478309</v>
+        <v>478104</v>
       </c>
       <c r="R6" t="n">
-        <v>6820751</v>
+        <v>6821165</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1183,7 +1188,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1193,7 +1198,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1220,7 +1225,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127445814</v>
+        <v>127442809</v>
       </c>
       <c r="B7" t="n">
         <v>79018</v>
@@ -1251,17 +1256,17 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Harabacken, Harabacken, Dlr</t>
+          <t>Kuusikallio, Kuusikallio, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>478096</v>
+        <v>478309</v>
       </c>
       <c r="R7" t="n">
-        <v>6821144</v>
+        <v>6820751</v>
       </c>
       <c r="S7" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1290,7 +1295,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1300,7 +1305,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1327,7 +1332,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127444509</v>
+        <v>127445814</v>
       </c>
       <c r="B8" t="n">
         <v>79018</v>
@@ -1358,17 +1363,17 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Harabacken, Dlr</t>
+          <t>Harabacken, Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>478229</v>
+        <v>478096</v>
       </c>
       <c r="R8" t="n">
-        <v>6821051</v>
+        <v>6821144</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1397,7 +1402,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1407,7 +1412,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1422,22 +1427,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127445695</v>
+        <v>127444509</v>
       </c>
       <c r="B9" t="n">
-        <v>57658</v>
+        <v>79018</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1445,42 +1450,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Harabacken, Harabacken, Dlr</t>
+          <t>Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>478104</v>
+        <v>478229</v>
       </c>
       <c r="R9" t="n">
-        <v>6821165</v>
+        <v>6821051</v>
       </c>
       <c r="S9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1519,7 +1519,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1534,22 +1534,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127444616</v>
+        <v>127447989</v>
       </c>
       <c r="B10" t="n">
-        <v>79050</v>
+        <v>79018</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1557,34 +1557,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Harabacken, Harabacken, Dlr</t>
+          <t>Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>478034</v>
+        <v>478360</v>
       </c>
       <c r="R10" t="n">
-        <v>6821199</v>
+        <v>6820946</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1616,7 +1616,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1641,22 +1641,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127447989</v>
+        <v>127444616</v>
       </c>
       <c r="B11" t="n">
-        <v>79018</v>
+        <v>79050</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1664,34 +1664,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Harabacken, Dlr</t>
+          <t>Harabacken, Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>478360</v>
+        <v>478034</v>
       </c>
       <c r="R11" t="n">
-        <v>6820946</v>
+        <v>6821199</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1723,7 +1723,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1733,7 +1733,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1748,12 +1748,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander, Håkan Thenander, Bo karlstens, Birgitta Kvist, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1872,32 +1872,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127444817</v>
+        <v>127443080</v>
       </c>
       <c r="B13" t="n">
-        <v>79050</v>
+        <v>98364</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>185</v>
+        <v>219790</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1907,13 +1907,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>478071</v>
+        <v>478309</v>
       </c>
       <c r="R13" t="n">
-        <v>6821227</v>
+        <v>6820751</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1952,12 +1952,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:22</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>På gran</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1972,44 +1967,44 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127443080</v>
+        <v>127444817</v>
       </c>
       <c r="B14" t="n">
-        <v>98364</v>
+        <v>79050</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219790</v>
+        <v>185</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2019,13 +2014,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>478309</v>
+        <v>478071</v>
       </c>
       <c r="R14" t="n">
-        <v>6820751</v>
+        <v>6821227</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2054,7 +2049,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2064,7 +2059,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2079,12 +2079,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Bo karlstens, Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Birgitta Kvist, Bengt Oldhammer, Bo karlstens</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2410,7 +2410,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
+          <t>Peter Turander, Håkan Thenander, Bo karlstens, Birgitta Kvist, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2838,7 +2838,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
+          <t>Peter Turander, Håkan Thenander, Bo karlstens, Birgitta Kvist, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -2952,10 +2952,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127444809</v>
+        <v>127443690</v>
       </c>
       <c r="B23" t="n">
-        <v>79018</v>
+        <v>57658</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2963,37 +2963,42 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Harabacken, Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>478062</v>
+        <v>478071</v>
       </c>
       <c r="R23" t="n">
-        <v>6821226</v>
+        <v>6821124</v>
       </c>
       <c r="S23" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3022,7 +3027,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3032,7 +3037,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3047,22 +3052,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Bo karlstens, Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127443315</v>
+        <v>127444600</v>
       </c>
       <c r="B24" t="n">
-        <v>79018</v>
+        <v>57658</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3070,37 +3075,42 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Harabacken, Dlr</t>
+          <t>Harabacken, Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>478109</v>
+        <v>478030</v>
       </c>
       <c r="R24" t="n">
-        <v>6820979</v>
+        <v>6821197</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3129,7 +3139,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3139,7 +3149,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3154,22 +3164,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander, Håkan Thenander, Bo karlstens, Birgitta Kvist, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127443690</v>
+        <v>127444809</v>
       </c>
       <c r="B25" t="n">
-        <v>57658</v>
+        <v>79018</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3177,42 +3187,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Harabacken, Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>478071</v>
+        <v>478062</v>
       </c>
       <c r="R25" t="n">
-        <v>6821124</v>
+        <v>6821226</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3241,7 +3246,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3251,7 +3256,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3266,22 +3271,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
+          <t>Bo karlstens, Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127444600</v>
+        <v>127443315</v>
       </c>
       <c r="B26" t="n">
-        <v>57658</v>
+        <v>79018</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3289,42 +3294,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Harabacken, Harabacken, Dlr</t>
+          <t>Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>478030</v>
+        <v>478109</v>
       </c>
       <c r="R26" t="n">
-        <v>6821197</v>
+        <v>6820979</v>
       </c>
       <c r="S26" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3353,7 +3353,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3363,7 +3363,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3378,22 +3378,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127445612</v>
+        <v>127451855</v>
       </c>
       <c r="B27" t="n">
-        <v>79018</v>
+        <v>79050</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3401,37 +3401,40 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>478265</v>
+        <v>478077</v>
       </c>
       <c r="R27" t="n">
-        <v>6821033</v>
+        <v>6820974</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3458,19 +3461,14 @@
           <t>2025-08-13</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>10:20</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-08-13</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>10:20</t>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3479,28 +3477,29 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127445678</v>
+        <v>127445612</v>
       </c>
       <c r="B28" t="n">
-        <v>57661</v>
+        <v>79018</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3508,42 +3507,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Kuusikallio, Kuusikallio, Dlr</t>
+          <t>Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>478106</v>
+        <v>478265</v>
       </c>
       <c r="R28" t="n">
-        <v>6821168</v>
+        <v>6821033</v>
       </c>
       <c r="S28" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3572,7 +3566,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3582,7 +3576,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3597,22 +3591,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127451855</v>
+        <v>127445678</v>
       </c>
       <c r="B29" t="n">
-        <v>79050</v>
+        <v>57661</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3620,40 +3614,42 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Harabacken, Dlr</t>
+          <t>Kuusikallio, Kuusikallio, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>478077</v>
+        <v>478106</v>
       </c>
       <c r="R29" t="n">
-        <v>6820974</v>
+        <v>6821168</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3680,14 +3676,19 @@
           <t>2025-08-13</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-08-13</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>På gran</t>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3696,19 +3697,18 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -3822,10 +3822,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127445756</v>
+        <v>127441057</v>
       </c>
       <c r="B31" t="n">
-        <v>79018</v>
+        <v>57658</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3833,37 +3833,42 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Harabacken, Harabacken, Dlr</t>
+          <t>Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>478104</v>
+        <v>478319</v>
       </c>
       <c r="R31" t="n">
-        <v>6821165</v>
+        <v>6820790</v>
       </c>
       <c r="S31" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3892,7 +3897,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3902,7 +3907,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3917,22 +3922,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127441057</v>
+        <v>127445756</v>
       </c>
       <c r="B32" t="n">
-        <v>57658</v>
+        <v>79018</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3940,42 +3945,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Harabacken, Dlr</t>
+          <t>Harabacken, Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>478319</v>
+        <v>478104</v>
       </c>
       <c r="R32" t="n">
-        <v>6820790</v>
+        <v>6821165</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4004,7 +4004,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4014,7 +4014,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4029,22 +4029,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127444793</v>
+        <v>127444491</v>
       </c>
       <c r="B33" t="n">
-        <v>57821</v>
+        <v>79050</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4052,42 +4052,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103021</v>
+        <v>185</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Harabacken, Dlr</t>
+          <t>Harabacken, Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>478245</v>
+        <v>478062</v>
       </c>
       <c r="R33" t="n">
-        <v>6821068</v>
+        <v>6821201</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4116,7 +4111,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4126,7 +4121,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Sparsamt på gran</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4141,19 +4141,19 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127444491</v>
+        <v>127444374</v>
       </c>
       <c r="B34" t="n">
         <v>79050</v>
@@ -4188,13 +4188,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>478062</v>
+        <v>478068</v>
       </c>
       <c r="R34" t="n">
-        <v>6821201</v>
+        <v>6821169</v>
       </c>
       <c r="S34" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4233,12 +4233,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:07</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Sparsamt på gran</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4253,22 +4248,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127444374</v>
+        <v>127444793</v>
       </c>
       <c r="B35" t="n">
-        <v>79050</v>
+        <v>57821</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4276,34 +4271,39 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>185</v>
+        <v>103021</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Harabacken, Harabacken, Dlr</t>
+          <t>Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>478068</v>
+        <v>478245</v>
       </c>
       <c r="R35" t="n">
-        <v>6821169</v>
+        <v>6821068</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4335,7 +4335,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4345,7 +4345,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4360,12 +4360,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -5355,53 +5355,48 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127443685</v>
+        <v>127443816</v>
       </c>
       <c r="B45" t="n">
-        <v>58031</v>
+        <v>79050</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>103015</v>
+        <v>185</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Harabacken, Dlr</t>
+          <t>Harabacken, Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>478128</v>
+        <v>478071</v>
       </c>
       <c r="R45" t="n">
-        <v>6820965</v>
+        <v>6821147</v>
       </c>
       <c r="S45" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5430,7 +5425,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5440,7 +5435,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5455,19 +5450,19 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127443816</v>
+        <v>127443715</v>
       </c>
       <c r="B46" t="n">
         <v>79050</v>
@@ -5498,14 +5493,14 @@
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Harabacken, Harabacken, Dlr</t>
+          <t>Kuusikallio, Kuusikallio, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>478071</v>
+        <v>478069</v>
       </c>
       <c r="R46" t="n">
-        <v>6821147</v>
+        <v>6821132</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5537,7 +5532,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5547,7 +5542,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5574,10 +5569,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127443715</v>
+        <v>127444469</v>
       </c>
       <c r="B47" t="n">
-        <v>79050</v>
+        <v>79018</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5585,34 +5580,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Kuusikallio, Kuusikallio, Dlr</t>
+          <t>Harabacken, Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>478069</v>
+        <v>478048</v>
       </c>
       <c r="R47" t="n">
-        <v>6821132</v>
+        <v>6821183</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5644,7 +5639,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5654,7 +5649,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5681,7 +5676,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127444469</v>
+        <v>127445040</v>
       </c>
       <c r="B48" t="n">
         <v>79018</v>
@@ -5716,13 +5711,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>478048</v>
+        <v>478072</v>
       </c>
       <c r="R48" t="n">
-        <v>6821183</v>
+        <v>6821204</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5751,7 +5746,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5761,7 +5756,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5776,60 +5776,65 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127445040</v>
+        <v>127443685</v>
       </c>
       <c r="B49" t="n">
-        <v>79018</v>
+        <v>58031</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Harabacken, Harabacken, Dlr</t>
+          <t>Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>478072</v>
+        <v>478128</v>
       </c>
       <c r="R49" t="n">
-        <v>6821204</v>
+        <v>6820965</v>
       </c>
       <c r="S49" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5858,7 +5863,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5868,12 +5873,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>12:22</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>På tall</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5888,22 +5888,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127444902</v>
+        <v>127443980</v>
       </c>
       <c r="B50" t="n">
-        <v>79050</v>
+        <v>79018</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5911,37 +5911,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Harabacken, Harabacken, Dlr</t>
+          <t>Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>478072</v>
+        <v>478207</v>
       </c>
       <c r="R50" t="n">
-        <v>6821204</v>
+        <v>6821016</v>
       </c>
       <c r="S50" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5970,7 +5970,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5980,12 +5980,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:22</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>På gran</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6000,22 +5995,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127443980</v>
+        <v>127444902</v>
       </c>
       <c r="B51" t="n">
-        <v>79018</v>
+        <v>79050</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6023,37 +6018,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Harabacken, Dlr</t>
+          <t>Harabacken, Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>478207</v>
+        <v>478072</v>
       </c>
       <c r="R51" t="n">
-        <v>6821016</v>
+        <v>6821204</v>
       </c>
       <c r="S51" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6082,7 +6077,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6092,7 +6087,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6107,12 +6107,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>

--- a/artfynd/A 33533-2025 artfynd.xlsx
+++ b/artfynd/A 33533-2025 artfynd.xlsx
@@ -2845,10 +2845,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127443809</v>
+        <v>127443690</v>
       </c>
       <c r="B22" t="n">
-        <v>79050</v>
+        <v>57658</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2856,37 +2856,42 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>185</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Harabacken, Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>478054</v>
+        <v>478071</v>
       </c>
       <c r="R22" t="n">
-        <v>6821168</v>
+        <v>6821124</v>
       </c>
       <c r="S22" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2915,7 +2920,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2925,7 +2930,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2940,19 +2945,19 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127443690</v>
+        <v>127444600</v>
       </c>
       <c r="B23" t="n">
         <v>57658</v>
@@ -2992,13 +2997,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>478071</v>
+        <v>478030</v>
       </c>
       <c r="R23" t="n">
-        <v>6821124</v>
+        <v>6821197</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3027,7 +3032,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3037,7 +3042,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3057,17 +3062,17 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
+          <t>Peter Turander, Håkan Thenander, Bo karlstens, Birgitta Kvist, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127444600</v>
+        <v>127444809</v>
       </c>
       <c r="B24" t="n">
-        <v>57658</v>
+        <v>79018</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3075,39 +3080,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Harabacken, Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>478030</v>
+        <v>478062</v>
       </c>
       <c r="R24" t="n">
-        <v>6821197</v>
+        <v>6821226</v>
       </c>
       <c r="S24" t="n">
         <v>9</v>
@@ -3139,7 +3139,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3149,7 +3149,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3164,19 +3164,19 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Peter Turander, Håkan Thenander, Bo karlstens, Birgitta Kvist, Bengt Oldhammer</t>
+          <t>Bo karlstens, Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127444809</v>
+        <v>127443315</v>
       </c>
       <c r="B25" t="n">
         <v>79018</v>
@@ -3207,17 +3207,17 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Harabacken, Harabacken, Dlr</t>
+          <t>Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>478062</v>
+        <v>478109</v>
       </c>
       <c r="R25" t="n">
-        <v>6821226</v>
+        <v>6820979</v>
       </c>
       <c r="S25" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3246,7 +3246,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3256,7 +3256,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3271,22 +3271,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Bo karlstens, Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127443315</v>
+        <v>127443809</v>
       </c>
       <c r="B26" t="n">
-        <v>79018</v>
+        <v>79050</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3294,37 +3294,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Harabacken, Dlr</t>
+          <t>Harabacken, Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>478109</v>
+        <v>478054</v>
       </c>
       <c r="R26" t="n">
-        <v>6820979</v>
+        <v>6821168</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3353,7 +3353,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3363,7 +3363,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3378,12 +3378,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3715,10 +3715,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127443983</v>
+        <v>127441057</v>
       </c>
       <c r="B30" t="n">
-        <v>91330</v>
+        <v>57658</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3726,37 +3726,42 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Kuusikallio, Kuusikallio, Dlr</t>
+          <t>Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>478068</v>
+        <v>478319</v>
       </c>
       <c r="R30" t="n">
-        <v>6821169</v>
+        <v>6820790</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3785,7 +3790,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3795,7 +3800,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3810,22 +3815,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127441057</v>
+        <v>127445756</v>
       </c>
       <c r="B31" t="n">
-        <v>57658</v>
+        <v>79018</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3833,42 +3838,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Harabacken, Dlr</t>
+          <t>Harabacken, Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>478319</v>
+        <v>478104</v>
       </c>
       <c r="R31" t="n">
-        <v>6820790</v>
+        <v>6821165</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3897,7 +3897,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3907,7 +3907,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3922,22 +3922,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127445756</v>
+        <v>127443983</v>
       </c>
       <c r="B32" t="n">
-        <v>79018</v>
+        <v>91330</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3945,37 +3945,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Harabacken, Harabacken, Dlr</t>
+          <t>Kuusikallio, Kuusikallio, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>478104</v>
+        <v>478068</v>
       </c>
       <c r="R32" t="n">
-        <v>6821165</v>
+        <v>6821169</v>
       </c>
       <c r="S32" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4004,7 +4004,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4014,7 +4014,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD32" t="b">

--- a/artfynd/A 33533-2025 artfynd.xlsx
+++ b/artfynd/A 33533-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127443978</v>
+        <v>127445512</v>
       </c>
       <c r="B2" t="n">
-        <v>75142</v>
+        <v>79018</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Harabacken, Dlr</t>
+          <t>Harabacken, Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>478207</v>
+        <v>478104</v>
       </c>
       <c r="R2" t="n">
-        <v>6821016</v>
+        <v>6821179</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,12 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:20</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Vitgrynig nållav på äldre gran</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,19 +770,19 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens, Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127445512</v>
+        <v>127445652</v>
       </c>
       <c r="B3" t="n">
         <v>79018</v>
@@ -818,17 +813,17 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Harabacken, Harabacken, Dlr</t>
+          <t>Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>478104</v>
+        <v>478270</v>
       </c>
       <c r="R3" t="n">
-        <v>6821179</v>
+        <v>6821004</v>
       </c>
       <c r="S3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -882,22 +877,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Bo karlstens, Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127445652</v>
+        <v>127443978</v>
       </c>
       <c r="B4" t="n">
-        <v>79018</v>
+        <v>75142</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -905,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,13 +924,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>478270</v>
+        <v>478207</v>
       </c>
       <c r="R4" t="n">
-        <v>6821004</v>
+        <v>6821016</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -975,6 +970,11 @@
       <c r="AB4" t="inlineStr">
         <is>
           <t>10:20</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav på äldre gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -2524,10 +2524,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127442676</v>
+        <v>127444686</v>
       </c>
       <c r="B19" t="n">
-        <v>79018</v>
+        <v>79050</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2535,21 +2535,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2559,10 +2559,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>478059</v>
+        <v>478062</v>
       </c>
       <c r="R19" t="n">
-        <v>6820931</v>
+        <v>6821226</v>
       </c>
       <c r="S19" t="n">
         <v>9</v>
@@ -2594,7 +2594,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2619,19 +2619,19 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Bo karlstens, Birgitta Kvist, Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127444686</v>
+        <v>127444556</v>
       </c>
       <c r="B20" t="n">
         <v>79050</v>
@@ -2666,10 +2666,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>478062</v>
+        <v>478030</v>
       </c>
       <c r="R20" t="n">
-        <v>6821226</v>
+        <v>6821197</v>
       </c>
       <c r="S20" t="n">
         <v>9</v>
@@ -2701,7 +2701,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2711,7 +2711,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2731,17 +2731,17 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
+          <t>Peter Turander, Håkan Thenander, Bo karlstens, Birgitta Kvist, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127444556</v>
+        <v>127442676</v>
       </c>
       <c r="B21" t="n">
-        <v>79050</v>
+        <v>79018</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2749,21 +2749,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2773,10 +2773,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>478030</v>
+        <v>478059</v>
       </c>
       <c r="R21" t="n">
-        <v>6821197</v>
+        <v>6820931</v>
       </c>
       <c r="S21" t="n">
         <v>9</v>
@@ -2808,7 +2808,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2818,7 +2818,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2833,12 +2833,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Peter Turander, Håkan Thenander, Bo karlstens, Birgitta Kvist, Bengt Oldhammer</t>
+          <t>Bo karlstens, Birgitta Kvist, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -3390,10 +3390,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127451855</v>
+        <v>127445612</v>
       </c>
       <c r="B27" t="n">
-        <v>79050</v>
+        <v>79018</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3401,40 +3401,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>478077</v>
+        <v>478265</v>
       </c>
       <c r="R27" t="n">
-        <v>6820974</v>
+        <v>6821033</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3461,14 +3458,19 @@
           <t>2025-08-13</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-08-13</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>På gran</t>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3477,29 +3479,28 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127445612</v>
+        <v>127445678</v>
       </c>
       <c r="B28" t="n">
-        <v>79018</v>
+        <v>57661</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3507,37 +3508,42 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Harabacken, Dlr</t>
+          <t>Kuusikallio, Kuusikallio, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>478265</v>
+        <v>478106</v>
       </c>
       <c r="R28" t="n">
-        <v>6821033</v>
+        <v>6821168</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3566,7 +3572,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3576,7 +3582,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3591,22 +3597,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127445678</v>
+        <v>127451855</v>
       </c>
       <c r="B29" t="n">
-        <v>57661</v>
+        <v>79050</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3614,42 +3620,40 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Kuusikallio, Kuusikallio, Dlr</t>
+          <t>Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>478106</v>
+        <v>478077</v>
       </c>
       <c r="R29" t="n">
-        <v>6821168</v>
+        <v>6820974</v>
       </c>
       <c r="S29" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3676,19 +3680,14 @@
           <t>2025-08-13</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>12:47</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-08-13</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>12:47</t>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3697,28 +3696,29 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127441057</v>
+        <v>127443983</v>
       </c>
       <c r="B30" t="n">
-        <v>57658</v>
+        <v>91330</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3726,42 +3726,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Harabacken, Dlr</t>
+          <t>Kuusikallio, Kuusikallio, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>478319</v>
+        <v>478068</v>
       </c>
       <c r="R30" t="n">
-        <v>6820790</v>
+        <v>6821169</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3790,7 +3785,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3800,7 +3795,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3815,22 +3810,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127445756</v>
+        <v>127441057</v>
       </c>
       <c r="B31" t="n">
-        <v>79018</v>
+        <v>57658</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3838,37 +3833,42 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Harabacken, Harabacken, Dlr</t>
+          <t>Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>478104</v>
+        <v>478319</v>
       </c>
       <c r="R31" t="n">
-        <v>6821165</v>
+        <v>6820790</v>
       </c>
       <c r="S31" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3897,7 +3897,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3907,7 +3907,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3922,22 +3922,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127443983</v>
+        <v>127445756</v>
       </c>
       <c r="B32" t="n">
-        <v>91330</v>
+        <v>79018</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3945,37 +3945,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Kuusikallio, Kuusikallio, Dlr</t>
+          <t>Harabacken, Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>478068</v>
+        <v>478104</v>
       </c>
       <c r="R32" t="n">
-        <v>6821169</v>
+        <v>6821165</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4004,7 +4004,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4014,7 +4014,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4041,10 +4041,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127444491</v>
+        <v>127444793</v>
       </c>
       <c r="B33" t="n">
-        <v>79050</v>
+        <v>57821</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4052,37 +4052,42 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>185</v>
+        <v>103021</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Harabacken, Harabacken, Dlr</t>
+          <t>Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>478062</v>
+        <v>478245</v>
       </c>
       <c r="R33" t="n">
-        <v>6821201</v>
+        <v>6821068</v>
       </c>
       <c r="S33" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4111,7 +4116,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4121,12 +4126,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:07</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Sparsamt på gran</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4141,19 +4141,19 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127444374</v>
+        <v>127444491</v>
       </c>
       <c r="B34" t="n">
         <v>79050</v>
@@ -4188,13 +4188,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>478068</v>
+        <v>478062</v>
       </c>
       <c r="R34" t="n">
-        <v>6821169</v>
+        <v>6821201</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4233,7 +4233,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Sparsamt på gran</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4248,22 +4253,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127444793</v>
+        <v>127444374</v>
       </c>
       <c r="B35" t="n">
-        <v>57821</v>
+        <v>79050</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4271,39 +4276,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103021</v>
+        <v>185</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Harabacken, Dlr</t>
+          <t>Harabacken, Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>478245</v>
+        <v>478068</v>
       </c>
       <c r="R35" t="n">
-        <v>6821068</v>
+        <v>6821169</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4335,7 +4335,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4345,7 +4345,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4360,12 +4360,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>

--- a/artfynd/A 33533-2025 artfynd.xlsx
+++ b/artfynd/A 33533-2025 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127445652</v>
+        <v>127443978</v>
       </c>
       <c r="B3" t="n">
-        <v>79018</v>
+        <v>75142</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>478270</v>
+        <v>478207</v>
       </c>
       <c r="R3" t="n">
-        <v>6821004</v>
+        <v>6821016</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -863,6 +863,11 @@
       <c r="AB3" t="inlineStr">
         <is>
           <t>10:20</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav på äldre gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127443978</v>
+        <v>127445652</v>
       </c>
       <c r="B4" t="n">
-        <v>75142</v>
+        <v>79018</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,13 +929,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>478207</v>
+        <v>478270</v>
       </c>
       <c r="R4" t="n">
-        <v>6821016</v>
+        <v>6821004</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -970,11 +975,6 @@
       <c r="AB4" t="inlineStr">
         <is>
           <t>10:20</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Vitgrynig nållav på äldre gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1113,10 +1113,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127445695</v>
+        <v>127442809</v>
       </c>
       <c r="B6" t="n">
-        <v>57658</v>
+        <v>79018</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1124,42 +1124,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Harabacken, Harabacken, Dlr</t>
+          <t>Kuusikallio, Kuusikallio, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>478104</v>
+        <v>478309</v>
       </c>
       <c r="R6" t="n">
-        <v>6821165</v>
+        <v>6820751</v>
       </c>
       <c r="S6" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1188,7 +1183,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1198,7 +1193,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1225,7 +1220,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127442809</v>
+        <v>127445814</v>
       </c>
       <c r="B7" t="n">
         <v>79018</v>
@@ -1256,17 +1251,17 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kuusikallio, Kuusikallio, Dlr</t>
+          <t>Harabacken, Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>478309</v>
+        <v>478096</v>
       </c>
       <c r="R7" t="n">
-        <v>6820751</v>
+        <v>6821144</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1295,7 +1290,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1305,7 +1300,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1332,7 +1327,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127445814</v>
+        <v>127444509</v>
       </c>
       <c r="B8" t="n">
         <v>79018</v>
@@ -1363,17 +1358,17 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Harabacken, Harabacken, Dlr</t>
+          <t>Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>478096</v>
+        <v>478229</v>
       </c>
       <c r="R8" t="n">
-        <v>6821144</v>
+        <v>6821051</v>
       </c>
       <c r="S8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1402,7 +1397,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1412,7 +1407,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1427,22 +1422,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127444509</v>
+        <v>127445695</v>
       </c>
       <c r="B9" t="n">
-        <v>79018</v>
+        <v>57658</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1450,37 +1445,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Harabacken, Dlr</t>
+          <t>Harabacken, Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>478229</v>
+        <v>478104</v>
       </c>
       <c r="R9" t="n">
-        <v>6821051</v>
+        <v>6821165</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1519,7 +1519,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1534,22 +1534,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127447989</v>
+        <v>127444616</v>
       </c>
       <c r="B10" t="n">
-        <v>79018</v>
+        <v>79050</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1557,34 +1557,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Harabacken, Dlr</t>
+          <t>Harabacken, Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>478360</v>
+        <v>478034</v>
       </c>
       <c r="R10" t="n">
-        <v>6820946</v>
+        <v>6821199</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1616,7 +1616,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1641,22 +1641,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127444616</v>
+        <v>127447989</v>
       </c>
       <c r="B11" t="n">
-        <v>79050</v>
+        <v>79018</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1664,34 +1664,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Harabacken, Harabacken, Dlr</t>
+          <t>Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>478034</v>
+        <v>478360</v>
       </c>
       <c r="R11" t="n">
-        <v>6821199</v>
+        <v>6820946</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1723,7 +1723,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1733,7 +1733,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1748,12 +1748,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Peter Turander, Håkan Thenander, Bo karlstens, Birgitta Kvist, Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1872,32 +1872,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127443080</v>
+        <v>127444817</v>
       </c>
       <c r="B13" t="n">
-        <v>98364</v>
+        <v>79050</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219790</v>
+        <v>185</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1907,13 +1907,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>478309</v>
+        <v>478071</v>
       </c>
       <c r="R13" t="n">
-        <v>6820751</v>
+        <v>6821227</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1952,7 +1952,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1967,44 +1972,44 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127444817</v>
+        <v>127443080</v>
       </c>
       <c r="B14" t="n">
-        <v>79050</v>
+        <v>98365</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>185</v>
+        <v>219790</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2014,13 +2019,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>478071</v>
+        <v>478309</v>
       </c>
       <c r="R14" t="n">
-        <v>6821227</v>
+        <v>6820751</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2049,7 +2054,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2059,12 +2064,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:22</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>På gran</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2079,12 +2079,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2198,10 +2198,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127444563</v>
+        <v>127444510</v>
       </c>
       <c r="B16" t="n">
-        <v>79050</v>
+        <v>57661</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2209,34 +2209,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Harabacken, Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>478024</v>
+        <v>478030</v>
       </c>
       <c r="R16" t="n">
-        <v>6821213</v>
+        <v>6821195</v>
       </c>
       <c r="S16" t="n">
         <v>9</v>
@@ -2268,7 +2273,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2278,7 +2283,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2293,22 +2298,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Birgitta Kvist, Bengt Oldhammer, Bo karlstens</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127444510</v>
+        <v>127444563</v>
       </c>
       <c r="B17" t="n">
-        <v>57661</v>
+        <v>79050</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2316,39 +2321,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Harabacken, Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>478030</v>
+        <v>478024</v>
       </c>
       <c r="R17" t="n">
-        <v>6821195</v>
+        <v>6821213</v>
       </c>
       <c r="S17" t="n">
         <v>9</v>
@@ -2380,7 +2380,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2390,7 +2390,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2405,12 +2405,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Peter Turander, Håkan Thenander, Bo karlstens, Birgitta Kvist, Bengt Oldhammer</t>
+          <t>Bo karlstens, Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2731,7 +2731,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Peter Turander, Håkan Thenander, Bo karlstens, Birgitta Kvist, Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2838,17 +2838,17 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Bo karlstens, Birgitta Kvist, Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127443690</v>
+        <v>127443809</v>
       </c>
       <c r="B22" t="n">
-        <v>57658</v>
+        <v>79050</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2856,42 +2856,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>185</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Harabacken, Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>478071</v>
+        <v>478054</v>
       </c>
       <c r="R22" t="n">
-        <v>6821124</v>
+        <v>6821168</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2920,7 +2915,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2930,7 +2925,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2945,22 +2940,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127444600</v>
+        <v>127444809</v>
       </c>
       <c r="B23" t="n">
-        <v>57658</v>
+        <v>79018</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2968,39 +2963,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Harabacken, Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>478030</v>
+        <v>478062</v>
       </c>
       <c r="R23" t="n">
-        <v>6821197</v>
+        <v>6821226</v>
       </c>
       <c r="S23" t="n">
         <v>9</v>
@@ -3032,7 +3022,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3042,7 +3032,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3057,19 +3047,19 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Peter Turander, Håkan Thenander, Bo karlstens, Birgitta Kvist, Bengt Oldhammer</t>
+          <t>Bo karlstens, Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127444809</v>
+        <v>127443315</v>
       </c>
       <c r="B24" t="n">
         <v>79018</v>
@@ -3100,17 +3090,17 @@
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Harabacken, Harabacken, Dlr</t>
+          <t>Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>478062</v>
+        <v>478109</v>
       </c>
       <c r="R24" t="n">
-        <v>6821226</v>
+        <v>6820979</v>
       </c>
       <c r="S24" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3139,7 +3129,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3149,7 +3139,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3164,22 +3154,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Bo karlstens, Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127443315</v>
+        <v>127443690</v>
       </c>
       <c r="B25" t="n">
-        <v>79018</v>
+        <v>57658</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3187,37 +3177,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Harabacken, Dlr</t>
+          <t>Harabacken, Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>478109</v>
+        <v>478071</v>
       </c>
       <c r="R25" t="n">
-        <v>6820979</v>
+        <v>6821124</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3246,7 +3241,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3256,7 +3251,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3271,22 +3266,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127443809</v>
+        <v>127444600</v>
       </c>
       <c r="B26" t="n">
-        <v>79050</v>
+        <v>57658</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3294,37 +3289,42 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>185</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Harabacken, Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>478054</v>
+        <v>478030</v>
       </c>
       <c r="R26" t="n">
-        <v>6821168</v>
+        <v>6821197</v>
       </c>
       <c r="S26" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3353,7 +3353,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3363,7 +3363,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3378,22 +3378,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127445612</v>
+        <v>127451855</v>
       </c>
       <c r="B27" t="n">
-        <v>79018</v>
+        <v>79050</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3401,37 +3401,40 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>478265</v>
+        <v>478077</v>
       </c>
       <c r="R27" t="n">
-        <v>6821033</v>
+        <v>6820974</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3458,19 +3461,14 @@
           <t>2025-08-13</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>10:20</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-08-13</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>10:20</t>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3479,28 +3477,29 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127445678</v>
+        <v>127445612</v>
       </c>
       <c r="B28" t="n">
-        <v>57661</v>
+        <v>79018</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3508,42 +3507,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Kuusikallio, Kuusikallio, Dlr</t>
+          <t>Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>478106</v>
+        <v>478265</v>
       </c>
       <c r="R28" t="n">
-        <v>6821168</v>
+        <v>6821033</v>
       </c>
       <c r="S28" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3572,7 +3566,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3582,7 +3576,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3597,22 +3591,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127451855</v>
+        <v>127445678</v>
       </c>
       <c r="B29" t="n">
-        <v>79050</v>
+        <v>57661</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3620,40 +3614,42 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Harabacken, Dlr</t>
+          <t>Kuusikallio, Kuusikallio, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>478077</v>
+        <v>478106</v>
       </c>
       <c r="R29" t="n">
-        <v>6820974</v>
+        <v>6821168</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3680,14 +3676,19 @@
           <t>2025-08-13</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-08-13</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>På gran</t>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3696,19 +3697,18 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -3822,10 +3822,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127441057</v>
+        <v>127445756</v>
       </c>
       <c r="B31" t="n">
-        <v>57658</v>
+        <v>79018</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3833,42 +3833,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Harabacken, Dlr</t>
+          <t>Harabacken, Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>478319</v>
+        <v>478104</v>
       </c>
       <c r="R31" t="n">
-        <v>6820790</v>
+        <v>6821165</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3897,7 +3892,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3907,7 +3902,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3922,22 +3917,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127445756</v>
+        <v>127441057</v>
       </c>
       <c r="B32" t="n">
-        <v>79018</v>
+        <v>57658</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3945,37 +3940,42 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Harabacken, Harabacken, Dlr</t>
+          <t>Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>478104</v>
+        <v>478319</v>
       </c>
       <c r="R32" t="n">
-        <v>6821165</v>
+        <v>6820790</v>
       </c>
       <c r="S32" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4004,7 +4004,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4014,7 +4014,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4029,22 +4029,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127444793</v>
+        <v>127444491</v>
       </c>
       <c r="B33" t="n">
-        <v>57821</v>
+        <v>79050</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4052,42 +4052,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103021</v>
+        <v>185</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Harabacken, Dlr</t>
+          <t>Harabacken, Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>478245</v>
+        <v>478062</v>
       </c>
       <c r="R33" t="n">
-        <v>6821068</v>
+        <v>6821201</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4116,7 +4111,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4126,7 +4121,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Sparsamt på gran</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4141,19 +4141,19 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127444491</v>
+        <v>127444374</v>
       </c>
       <c r="B34" t="n">
         <v>79050</v>
@@ -4188,13 +4188,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>478062</v>
+        <v>478068</v>
       </c>
       <c r="R34" t="n">
-        <v>6821201</v>
+        <v>6821169</v>
       </c>
       <c r="S34" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4233,12 +4233,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:07</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Sparsamt på gran</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4253,22 +4248,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127444374</v>
+        <v>127444793</v>
       </c>
       <c r="B35" t="n">
-        <v>79050</v>
+        <v>57821</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4276,34 +4271,39 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>185</v>
+        <v>103021</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Harabacken, Harabacken, Dlr</t>
+          <t>Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>478068</v>
+        <v>478245</v>
       </c>
       <c r="R35" t="n">
-        <v>6821169</v>
+        <v>6821068</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4335,7 +4335,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4345,7 +4345,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4360,12 +4360,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -5355,10 +5355,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127443816</v>
+        <v>127444469</v>
       </c>
       <c r="B45" t="n">
-        <v>79050</v>
+        <v>79018</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5366,21 +5366,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5390,10 +5390,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>478071</v>
+        <v>478048</v>
       </c>
       <c r="R45" t="n">
-        <v>6821147</v>
+        <v>6821183</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5462,10 +5462,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127443715</v>
+        <v>127445040</v>
       </c>
       <c r="B46" t="n">
-        <v>79050</v>
+        <v>79018</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5473,37 +5473,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Kuusikallio, Kuusikallio, Dlr</t>
+          <t>Harabacken, Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>478069</v>
+        <v>478072</v>
       </c>
       <c r="R46" t="n">
-        <v>6821132</v>
+        <v>6821204</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5532,7 +5532,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5542,7 +5542,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5557,60 +5562,65 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127444469</v>
+        <v>127443685</v>
       </c>
       <c r="B47" t="n">
-        <v>79018</v>
+        <v>58031</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Harabacken, Harabacken, Dlr</t>
+          <t>Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>478048</v>
+        <v>478128</v>
       </c>
       <c r="R47" t="n">
-        <v>6821183</v>
+        <v>6820965</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5639,7 +5649,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5649,7 +5659,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5664,22 +5674,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127445040</v>
+        <v>127443816</v>
       </c>
       <c r="B48" t="n">
-        <v>79018</v>
+        <v>79050</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5687,21 +5697,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5711,13 +5721,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>478072</v>
+        <v>478071</v>
       </c>
       <c r="R48" t="n">
-        <v>6821204</v>
+        <v>6821147</v>
       </c>
       <c r="S48" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5746,7 +5756,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5756,12 +5766,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:22</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>På tall</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5776,65 +5781,60 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127443685</v>
+        <v>127443715</v>
       </c>
       <c r="B49" t="n">
-        <v>58031</v>
+        <v>79050</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>103015</v>
+        <v>185</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Harabacken, Dlr</t>
+          <t>Kuusikallio, Kuusikallio, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>478128</v>
+        <v>478069</v>
       </c>
       <c r="R49" t="n">
-        <v>6820965</v>
+        <v>6821132</v>
       </c>
       <c r="S49" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5863,7 +5863,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5873,7 +5873,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5888,12 +5888,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>

--- a/artfynd/A 33533-2025 artfynd.xlsx
+++ b/artfynd/A 33533-2025 artfynd.xlsx
@@ -2198,10 +2198,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127444510</v>
+        <v>127444563</v>
       </c>
       <c r="B16" t="n">
-        <v>57661</v>
+        <v>79050</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2209,39 +2209,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Harabacken, Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>478030</v>
+        <v>478024</v>
       </c>
       <c r="R16" t="n">
-        <v>6821195</v>
+        <v>6821213</v>
       </c>
       <c r="S16" t="n">
         <v>9</v>
@@ -2273,7 +2268,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2283,7 +2278,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2298,22 +2293,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
+          <t>Bo karlstens, Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127444563</v>
+        <v>127444510</v>
       </c>
       <c r="B17" t="n">
-        <v>79050</v>
+        <v>57661</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2321,34 +2316,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Harabacken, Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>478024</v>
+        <v>478030</v>
       </c>
       <c r="R17" t="n">
-        <v>6821213</v>
+        <v>6821195</v>
       </c>
       <c r="S17" t="n">
         <v>9</v>
@@ -2380,7 +2380,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2390,7 +2390,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2405,12 +2405,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Bo karlstens, Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2845,10 +2845,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127443809</v>
+        <v>127443690</v>
       </c>
       <c r="B22" t="n">
-        <v>79050</v>
+        <v>57658</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2856,37 +2856,42 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>185</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Harabacken, Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>478054</v>
+        <v>478071</v>
       </c>
       <c r="R22" t="n">
-        <v>6821168</v>
+        <v>6821124</v>
       </c>
       <c r="S22" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2915,7 +2920,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2925,7 +2930,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2940,22 +2945,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127444809</v>
+        <v>127444600</v>
       </c>
       <c r="B23" t="n">
-        <v>79018</v>
+        <v>57658</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2963,34 +2968,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Harabacken, Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>478062</v>
+        <v>478030</v>
       </c>
       <c r="R23" t="n">
-        <v>6821226</v>
+        <v>6821197</v>
       </c>
       <c r="S23" t="n">
         <v>9</v>
@@ -3022,7 +3032,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3032,7 +3042,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3047,22 +3057,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Bo karlstens, Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127443315</v>
+        <v>127443809</v>
       </c>
       <c r="B24" t="n">
-        <v>79018</v>
+        <v>79050</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3070,37 +3080,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Harabacken, Dlr</t>
+          <t>Harabacken, Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>478109</v>
+        <v>478054</v>
       </c>
       <c r="R24" t="n">
-        <v>6820979</v>
+        <v>6821168</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3129,7 +3139,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3139,7 +3149,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3154,22 +3164,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127443690</v>
+        <v>127444809</v>
       </c>
       <c r="B25" t="n">
-        <v>57658</v>
+        <v>79018</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3177,42 +3187,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Harabacken, Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>478071</v>
+        <v>478062</v>
       </c>
       <c r="R25" t="n">
-        <v>6821124</v>
+        <v>6821226</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3241,7 +3246,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3251,7 +3256,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3266,22 +3271,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
+          <t>Bo karlstens, Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127444600</v>
+        <v>127443315</v>
       </c>
       <c r="B26" t="n">
-        <v>57658</v>
+        <v>79018</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3289,42 +3294,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Harabacken, Harabacken, Dlr</t>
+          <t>Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>478030</v>
+        <v>478109</v>
       </c>
       <c r="R26" t="n">
-        <v>6821197</v>
+        <v>6820979</v>
       </c>
       <c r="S26" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3353,7 +3353,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3363,7 +3363,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3378,12 +3378,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3715,10 +3715,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127443983</v>
+        <v>127445756</v>
       </c>
       <c r="B30" t="n">
-        <v>91330</v>
+        <v>79018</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3726,37 +3726,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Kuusikallio, Kuusikallio, Dlr</t>
+          <t>Harabacken, Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>478068</v>
+        <v>478104</v>
       </c>
       <c r="R30" t="n">
-        <v>6821169</v>
+        <v>6821165</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3785,7 +3785,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3795,7 +3795,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3822,10 +3822,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127445756</v>
+        <v>127441057</v>
       </c>
       <c r="B31" t="n">
-        <v>79018</v>
+        <v>57658</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3833,37 +3833,42 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Harabacken, Harabacken, Dlr</t>
+          <t>Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>478104</v>
+        <v>478319</v>
       </c>
       <c r="R31" t="n">
-        <v>6821165</v>
+        <v>6820790</v>
       </c>
       <c r="S31" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3892,7 +3897,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3902,7 +3907,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3917,22 +3922,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127441057</v>
+        <v>127443983</v>
       </c>
       <c r="B32" t="n">
-        <v>57658</v>
+        <v>91330</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3940,42 +3945,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Harabacken, Dlr</t>
+          <t>Kuusikallio, Kuusikallio, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>478319</v>
+        <v>478068</v>
       </c>
       <c r="R32" t="n">
-        <v>6820790</v>
+        <v>6821169</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4004,7 +4004,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4014,7 +4014,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4029,12 +4029,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -5355,48 +5355,53 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127444469</v>
+        <v>127443685</v>
       </c>
       <c r="B45" t="n">
-        <v>79018</v>
+        <v>58031</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Harabacken, Harabacken, Dlr</t>
+          <t>Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>478048</v>
+        <v>478128</v>
       </c>
       <c r="R45" t="n">
-        <v>6821183</v>
+        <v>6820965</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5425,7 +5430,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5435,7 +5440,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5450,22 +5455,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127445040</v>
+        <v>127443715</v>
       </c>
       <c r="B46" t="n">
-        <v>79018</v>
+        <v>79050</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5473,37 +5478,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Harabacken, Harabacken, Dlr</t>
+          <t>Kuusikallio, Kuusikallio, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>478072</v>
+        <v>478069</v>
       </c>
       <c r="R46" t="n">
-        <v>6821204</v>
+        <v>6821132</v>
       </c>
       <c r="S46" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5532,7 +5537,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5542,12 +5547,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:22</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>På tall</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5562,65 +5562,60 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127443685</v>
+        <v>127443816</v>
       </c>
       <c r="B47" t="n">
-        <v>58031</v>
+        <v>79050</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>103015</v>
+        <v>185</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Harabacken, Dlr</t>
+          <t>Harabacken, Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>478128</v>
+        <v>478071</v>
       </c>
       <c r="R47" t="n">
-        <v>6820965</v>
+        <v>6821147</v>
       </c>
       <c r="S47" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5649,7 +5644,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5659,7 +5654,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5674,22 +5669,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127443816</v>
+        <v>127444469</v>
       </c>
       <c r="B48" t="n">
-        <v>79050</v>
+        <v>79018</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5697,21 +5692,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5721,10 +5716,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>478071</v>
+        <v>478048</v>
       </c>
       <c r="R48" t="n">
-        <v>6821147</v>
+        <v>6821183</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5793,10 +5788,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127443715</v>
+        <v>127445040</v>
       </c>
       <c r="B49" t="n">
-        <v>79050</v>
+        <v>79018</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5804,37 +5799,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Kuusikallio, Kuusikallio, Dlr</t>
+          <t>Harabacken, Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>478069</v>
+        <v>478072</v>
       </c>
       <c r="R49" t="n">
-        <v>6821132</v>
+        <v>6821204</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5863,7 +5858,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5873,7 +5868,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5888,22 +5888,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127443980</v>
+        <v>127444902</v>
       </c>
       <c r="B50" t="n">
-        <v>79018</v>
+        <v>79050</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5911,37 +5911,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Harabacken, Dlr</t>
+          <t>Harabacken, Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>478207</v>
+        <v>478072</v>
       </c>
       <c r="R50" t="n">
-        <v>6821016</v>
+        <v>6821204</v>
       </c>
       <c r="S50" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5970,7 +5970,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5980,7 +5980,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5995,22 +6000,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127444902</v>
+        <v>127443980</v>
       </c>
       <c r="B51" t="n">
-        <v>79050</v>
+        <v>79018</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6018,37 +6023,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Harabacken, Harabacken, Dlr</t>
+          <t>Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>478072</v>
+        <v>478207</v>
       </c>
       <c r="R51" t="n">
-        <v>6821204</v>
+        <v>6821016</v>
       </c>
       <c r="S51" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6077,7 +6082,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6087,12 +6092,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:22</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>På gran</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6107,12 +6107,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>

--- a/artfynd/A 33533-2025 artfynd.xlsx
+++ b/artfynd/A 33533-2025 artfynd.xlsx
@@ -675,45 +675,50 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127445512</v>
+        <v>127444794</v>
       </c>
       <c r="B2" t="n">
-        <v>79018</v>
+        <v>5177</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Harabacken, Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>478104</v>
+        <v>478062</v>
       </c>
       <c r="R2" t="n">
-        <v>6821179</v>
+        <v>6821226</v>
       </c>
       <c r="S2" t="n">
         <v>9</v>
@@ -745,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,7 +780,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Bo karlstens, Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -785,7 +790,7 @@
         <v>127443978</v>
       </c>
       <c r="B3" t="n">
-        <v>75142</v>
+        <v>75144</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +902,7 @@
         <v>127445652</v>
       </c>
       <c r="B4" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,50 +1006,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127444794</v>
+        <v>127445512</v>
       </c>
       <c r="B5" t="n">
-        <v>5177</v>
+        <v>79020</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Harabacken, Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>478062</v>
+        <v>478104</v>
       </c>
       <c r="R5" t="n">
-        <v>6821226</v>
+        <v>6821179</v>
       </c>
       <c r="S5" t="n">
         <v>9</v>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bo karlstens, Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1116,7 +1116,7 @@
         <v>127442809</v>
       </c>
       <c r="B6" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>127445814</v>
       </c>
       <c r="B7" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
         <v>127444509</v>
       </c>
       <c r="B8" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>127445695</v>
       </c>
       <c r="B9" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,17 +1539,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
+          <t>Peter Turander, Håkan Thenander, Bo karlstens, Birgitta Kvist, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127444616</v>
+        <v>127447989</v>
       </c>
       <c r="B10" t="n">
-        <v>79050</v>
+        <v>79020</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1557,34 +1557,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Harabacken, Harabacken, Dlr</t>
+          <t>Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>478034</v>
+        <v>478360</v>
       </c>
       <c r="R10" t="n">
-        <v>6821199</v>
+        <v>6820946</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1616,7 +1616,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1641,22 +1641,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127447989</v>
+        <v>127442751</v>
       </c>
       <c r="B11" t="n">
-        <v>79018</v>
+        <v>57660</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1664,34 +1664,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>478360</v>
+        <v>478022</v>
       </c>
       <c r="R11" t="n">
-        <v>6820946</v>
+        <v>6820902</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1760,10 +1765,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127442751</v>
+        <v>127444616</v>
       </c>
       <c r="B12" t="n">
-        <v>57658</v>
+        <v>79052</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1771,39 +1776,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>185</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Harabacken, Dlr</t>
+          <t>Harabacken, Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>478022</v>
+        <v>478034</v>
       </c>
       <c r="R12" t="n">
-        <v>6820902</v>
+        <v>6821199</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1860,12 +1860,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander, Håkan Thenander, Bo karlstens, Birgitta Kvist, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1875,7 +1875,7 @@
         <v>127444817</v>
       </c>
       <c r="B13" t="n">
-        <v>79050</v>
+        <v>79052</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         <v>127443080</v>
       </c>
       <c r="B14" t="n">
-        <v>98365</v>
+        <v>98367</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         <v>127444484</v>
       </c>
       <c r="B15" t="n">
-        <v>79050</v>
+        <v>79052</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         <v>127444563</v>
       </c>
       <c r="B16" t="n">
-        <v>79050</v>
+        <v>79052</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Bo karlstens, Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Birgitta Kvist, Bengt Oldhammer, Bo karlstens</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2308,7 +2308,7 @@
         <v>127444510</v>
       </c>
       <c r="B17" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2524,10 +2524,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127444686</v>
+        <v>127442676</v>
       </c>
       <c r="B19" t="n">
-        <v>79050</v>
+        <v>79020</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2535,21 +2535,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2559,10 +2559,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>478062</v>
+        <v>478059</v>
       </c>
       <c r="R19" t="n">
-        <v>6821226</v>
+        <v>6820931</v>
       </c>
       <c r="S19" t="n">
         <v>9</v>
@@ -2594,7 +2594,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2619,22 +2619,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
+          <t>Bo karlstens, Birgitta Kvist, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127444556</v>
+        <v>127444686</v>
       </c>
       <c r="B20" t="n">
-        <v>79050</v>
+        <v>79052</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2666,10 +2666,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>478030</v>
+        <v>478062</v>
       </c>
       <c r="R20" t="n">
-        <v>6821197</v>
+        <v>6821226</v>
       </c>
       <c r="S20" t="n">
         <v>9</v>
@@ -2701,7 +2701,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2711,7 +2711,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2738,10 +2738,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127442676</v>
+        <v>127444556</v>
       </c>
       <c r="B21" t="n">
-        <v>79018</v>
+        <v>79052</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2749,21 +2749,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2773,10 +2773,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>478059</v>
+        <v>478030</v>
       </c>
       <c r="R21" t="n">
-        <v>6820931</v>
+        <v>6821197</v>
       </c>
       <c r="S21" t="n">
         <v>9</v>
@@ -2808,7 +2808,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2818,7 +2818,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2833,22 +2833,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens</t>
+          <t>Peter Turander, Håkan Thenander, Bo karlstens, Birgitta Kvist, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127443690</v>
+        <v>127444809</v>
       </c>
       <c r="B22" t="n">
-        <v>57658</v>
+        <v>79020</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2856,42 +2856,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Harabacken, Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>478071</v>
+        <v>478062</v>
       </c>
       <c r="R22" t="n">
-        <v>6821124</v>
+        <v>6821226</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2920,7 +2915,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2930,7 +2925,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2945,22 +2940,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
+          <t>Bo karlstens, Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127444600</v>
+        <v>127443315</v>
       </c>
       <c r="B23" t="n">
-        <v>57658</v>
+        <v>79020</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2968,42 +2963,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Harabacken, Harabacken, Dlr</t>
+          <t>Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>478030</v>
+        <v>478109</v>
       </c>
       <c r="R23" t="n">
-        <v>6821197</v>
+        <v>6820979</v>
       </c>
       <c r="S23" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3032,7 +3022,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3042,7 +3032,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3057,12 +3047,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -3072,7 +3062,7 @@
         <v>127443809</v>
       </c>
       <c r="B24" t="n">
-        <v>79050</v>
+        <v>79052</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3176,10 +3166,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127444809</v>
+        <v>127443690</v>
       </c>
       <c r="B25" t="n">
-        <v>79018</v>
+        <v>57660</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3187,37 +3177,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Harabacken, Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>478062</v>
+        <v>478071</v>
       </c>
       <c r="R25" t="n">
-        <v>6821226</v>
+        <v>6821124</v>
       </c>
       <c r="S25" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3246,7 +3241,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3256,7 +3251,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3271,22 +3266,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Bo karlstens, Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Peter Turander, Håkan Thenander, Bo karlstens, Birgitta Kvist, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127443315</v>
+        <v>127444600</v>
       </c>
       <c r="B26" t="n">
-        <v>79018</v>
+        <v>57660</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3294,37 +3289,42 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Harabacken, Dlr</t>
+          <t>Harabacken, Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>478109</v>
+        <v>478030</v>
       </c>
       <c r="R26" t="n">
-        <v>6820979</v>
+        <v>6821197</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3353,7 +3353,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3363,7 +3363,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3378,22 +3378,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander, Håkan Thenander, Bo karlstens, Birgitta Kvist, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127451855</v>
+        <v>127445612</v>
       </c>
       <c r="B27" t="n">
-        <v>79050</v>
+        <v>79020</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3401,40 +3401,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>478077</v>
+        <v>478265</v>
       </c>
       <c r="R27" t="n">
-        <v>6820974</v>
+        <v>6821033</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3461,14 +3458,19 @@
           <t>2025-08-13</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-08-13</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>På gran</t>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3477,29 +3479,28 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127445612</v>
+        <v>127445678</v>
       </c>
       <c r="B28" t="n">
-        <v>79018</v>
+        <v>57663</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3507,37 +3508,42 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Harabacken, Dlr</t>
+          <t>Kuusikallio, Kuusikallio, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>478265</v>
+        <v>478106</v>
       </c>
       <c r="R28" t="n">
-        <v>6821033</v>
+        <v>6821168</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3566,7 +3572,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3576,7 +3582,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3591,22 +3597,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander, Håkan Thenander, Bo karlstens, Birgitta Kvist, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127445678</v>
+        <v>127451855</v>
       </c>
       <c r="B29" t="n">
-        <v>57661</v>
+        <v>79052</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3614,42 +3620,40 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Kuusikallio, Kuusikallio, Dlr</t>
+          <t>Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>478106</v>
+        <v>478077</v>
       </c>
       <c r="R29" t="n">
-        <v>6821168</v>
+        <v>6820974</v>
       </c>
       <c r="S29" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3676,19 +3680,14 @@
           <t>2025-08-13</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>12:47</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-08-13</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>12:47</t>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3697,28 +3696,29 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127445756</v>
+        <v>127441057</v>
       </c>
       <c r="B30" t="n">
-        <v>79018</v>
+        <v>57660</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3726,37 +3726,42 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Harabacken, Harabacken, Dlr</t>
+          <t>Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>478104</v>
+        <v>478319</v>
       </c>
       <c r="R30" t="n">
-        <v>6821165</v>
+        <v>6820790</v>
       </c>
       <c r="S30" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3785,7 +3790,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3795,7 +3800,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3810,22 +3815,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127441057</v>
+        <v>127445756</v>
       </c>
       <c r="B31" t="n">
-        <v>57658</v>
+        <v>79020</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3833,42 +3838,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Harabacken, Dlr</t>
+          <t>Harabacken, Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>478319</v>
+        <v>478104</v>
       </c>
       <c r="R31" t="n">
-        <v>6820790</v>
+        <v>6821165</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3897,7 +3897,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3907,7 +3907,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3922,12 +3922,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -3937,7 +3937,7 @@
         <v>127443983</v>
       </c>
       <c r="B32" t="n">
-        <v>91330</v>
+        <v>91332</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4044,7 +4044,7 @@
         <v>127444491</v>
       </c>
       <c r="B33" t="n">
-        <v>79050</v>
+        <v>79052</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4156,7 +4156,7 @@
         <v>127444374</v>
       </c>
       <c r="B34" t="n">
-        <v>79050</v>
+        <v>79052</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4263,7 +4263,7 @@
         <v>127444793</v>
       </c>
       <c r="B35" t="n">
-        <v>57821</v>
+        <v>57823</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4375,7 +4375,7 @@
         <v>127444001</v>
       </c>
       <c r="B36" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4482,7 +4482,7 @@
         <v>127443762</v>
       </c>
       <c r="B37" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4594,7 +4594,7 @@
         <v>127444502</v>
       </c>
       <c r="B38" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4706,7 +4706,7 @@
         <v>127445635</v>
       </c>
       <c r="B39" t="n">
-        <v>79607</v>
+        <v>79609</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4813,7 +4813,7 @@
         <v>127443785</v>
       </c>
       <c r="B40" t="n">
-        <v>58031</v>
+        <v>58033</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4925,7 +4925,7 @@
         <v>127444767</v>
       </c>
       <c r="B41" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5029,10 +5029,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127443466</v>
+        <v>127444496</v>
       </c>
       <c r="B42" t="n">
-        <v>79018</v>
+        <v>75144</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5040,21 +5040,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5064,10 +5064,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>478105</v>
+        <v>478229</v>
       </c>
       <c r="R42" t="n">
-        <v>6820956</v>
+        <v>6821051</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5136,10 +5136,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127444496</v>
+        <v>127443466</v>
       </c>
       <c r="B43" t="n">
-        <v>75142</v>
+        <v>79020</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5147,21 +5147,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5171,10 +5171,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>478229</v>
+        <v>478105</v>
       </c>
       <c r="R43" t="n">
-        <v>6821051</v>
+        <v>6820956</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5246,7 +5246,7 @@
         <v>127444690</v>
       </c>
       <c r="B44" t="n">
-        <v>57821</v>
+        <v>57823</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5355,53 +5355,48 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127443685</v>
+        <v>127445040</v>
       </c>
       <c r="B45" t="n">
-        <v>58031</v>
+        <v>79020</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Harabacken, Dlr</t>
+          <t>Harabacken, Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>478128</v>
+        <v>478072</v>
       </c>
       <c r="R45" t="n">
-        <v>6820965</v>
+        <v>6821204</v>
       </c>
       <c r="S45" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5430,7 +5425,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5440,7 +5435,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5455,22 +5455,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127443715</v>
+        <v>127444469</v>
       </c>
       <c r="B46" t="n">
-        <v>79050</v>
+        <v>79020</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5478,34 +5478,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Kuusikallio, Kuusikallio, Dlr</t>
+          <t>Harabacken, Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>478069</v>
+        <v>478048</v>
       </c>
       <c r="R46" t="n">
-        <v>6821132</v>
+        <v>6821183</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5537,7 +5537,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5547,7 +5547,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5574,48 +5574,53 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127443816</v>
+        <v>127443685</v>
       </c>
       <c r="B47" t="n">
-        <v>79050</v>
+        <v>58033</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>185</v>
+        <v>103015</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Harabacken, Harabacken, Dlr</t>
+          <t>Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>478071</v>
+        <v>478128</v>
       </c>
       <c r="R47" t="n">
-        <v>6821147</v>
+        <v>6820965</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5644,7 +5649,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5654,7 +5659,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5669,22 +5674,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127444469</v>
+        <v>127443816</v>
       </c>
       <c r="B48" t="n">
-        <v>79018</v>
+        <v>79052</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5692,21 +5697,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5716,10 +5721,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>478048</v>
+        <v>478071</v>
       </c>
       <c r="R48" t="n">
-        <v>6821183</v>
+        <v>6821147</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5788,10 +5793,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127445040</v>
+        <v>127443715</v>
       </c>
       <c r="B49" t="n">
-        <v>79018</v>
+        <v>79052</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5799,37 +5804,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Harabacken, Harabacken, Dlr</t>
+          <t>Kuusikallio, Kuusikallio, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>478072</v>
+        <v>478069</v>
       </c>
       <c r="R49" t="n">
-        <v>6821204</v>
+        <v>6821132</v>
       </c>
       <c r="S49" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5858,7 +5863,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5868,12 +5873,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>12:22</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>På tall</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5888,22 +5888,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127444902</v>
+        <v>127443980</v>
       </c>
       <c r="B50" t="n">
-        <v>79050</v>
+        <v>79020</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5911,37 +5911,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Harabacken, Harabacken, Dlr</t>
+          <t>Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>478072</v>
+        <v>478207</v>
       </c>
       <c r="R50" t="n">
-        <v>6821204</v>
+        <v>6821016</v>
       </c>
       <c r="S50" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5970,7 +5970,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5980,12 +5980,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:22</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>På gran</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6000,22 +5995,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127443980</v>
+        <v>127444902</v>
       </c>
       <c r="B51" t="n">
-        <v>79018</v>
+        <v>79052</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6023,37 +6018,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Harabacken, Dlr</t>
+          <t>Harabacken, Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>478207</v>
+        <v>478072</v>
       </c>
       <c r="R51" t="n">
-        <v>6821016</v>
+        <v>6821204</v>
       </c>
       <c r="S51" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6082,7 +6077,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6092,7 +6087,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6107,12 +6107,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
@@ -6122,7 +6122,7 @@
         <v>127442782</v>
       </c>
       <c r="B52" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>

--- a/artfynd/A 33533-2025 artfynd.xlsx
+++ b/artfynd/A 33533-2025 artfynd.xlsx
@@ -675,50 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127444794</v>
+        <v>127445512</v>
       </c>
       <c r="B2" t="n">
-        <v>5177</v>
+        <v>79020</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Harabacken, Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>478062</v>
+        <v>478104</v>
       </c>
       <c r="R2" t="n">
-        <v>6821226</v>
+        <v>6821179</v>
       </c>
       <c r="S2" t="n">
         <v>9</v>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,7 +775,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bo karlstens, Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -1006,45 +1001,50 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127445512</v>
+        <v>127444794</v>
       </c>
       <c r="B5" t="n">
-        <v>79020</v>
+        <v>5177</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Harabacken, Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>478104</v>
+        <v>478062</v>
       </c>
       <c r="R5" t="n">
-        <v>6821179</v>
+        <v>6821226</v>
       </c>
       <c r="S5" t="n">
         <v>9</v>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Bo karlstens, Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1539,17 +1539,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Peter Turander, Håkan Thenander, Bo karlstens, Birgitta Kvist, Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127447989</v>
+        <v>127444616</v>
       </c>
       <c r="B10" t="n">
-        <v>79020</v>
+        <v>79052</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1557,34 +1557,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Harabacken, Dlr</t>
+          <t>Harabacken, Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>478360</v>
+        <v>478034</v>
       </c>
       <c r="R10" t="n">
-        <v>6820946</v>
+        <v>6821199</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1616,7 +1616,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1641,22 +1641,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander, Håkan Thenander, Bo karlstens, Birgitta Kvist, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127442751</v>
+        <v>127447989</v>
       </c>
       <c r="B11" t="n">
-        <v>57660</v>
+        <v>79020</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1664,39 +1664,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>478022</v>
+        <v>478360</v>
       </c>
       <c r="R11" t="n">
-        <v>6820902</v>
+        <v>6820946</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1765,10 +1760,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127444616</v>
+        <v>127442751</v>
       </c>
       <c r="B12" t="n">
-        <v>79052</v>
+        <v>57660</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1776,34 +1771,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>185</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Harabacken, Harabacken, Dlr</t>
+          <t>Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>478034</v>
+        <v>478022</v>
       </c>
       <c r="R12" t="n">
-        <v>6821199</v>
+        <v>6820902</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1860,12 +1860,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Peter Turander, Håkan Thenander, Bo karlstens, Birgitta Kvist, Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -2198,10 +2198,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127444563</v>
+        <v>127444510</v>
       </c>
       <c r="B16" t="n">
-        <v>79052</v>
+        <v>57663</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2209,34 +2209,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Harabacken, Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>478024</v>
+        <v>478030</v>
       </c>
       <c r="R16" t="n">
-        <v>6821213</v>
+        <v>6821195</v>
       </c>
       <c r="S16" t="n">
         <v>9</v>
@@ -2268,7 +2273,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2278,7 +2283,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2293,22 +2298,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Birgitta Kvist, Bengt Oldhammer, Bo karlstens</t>
+          <t>Peter Turander, Håkan Thenander, Bo karlstens, Birgitta Kvist, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127444510</v>
+        <v>127444563</v>
       </c>
       <c r="B17" t="n">
-        <v>57663</v>
+        <v>79052</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2316,39 +2321,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Harabacken, Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>478030</v>
+        <v>478024</v>
       </c>
       <c r="R17" t="n">
-        <v>6821195</v>
+        <v>6821213</v>
       </c>
       <c r="S17" t="n">
         <v>9</v>
@@ -2380,7 +2380,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2390,7 +2390,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2405,12 +2405,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
+          <t>Birgitta Kvist, Bengt Oldhammer, Bo karlstens</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2845,10 +2845,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127444809</v>
+        <v>127443809</v>
       </c>
       <c r="B22" t="n">
-        <v>79020</v>
+        <v>79052</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2856,21 +2856,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2880,13 +2880,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>478062</v>
+        <v>478054</v>
       </c>
       <c r="R22" t="n">
-        <v>6821226</v>
+        <v>6821168</v>
       </c>
       <c r="S22" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2915,7 +2915,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2925,7 +2925,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2940,19 +2940,19 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Bo karlstens, Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127443315</v>
+        <v>127444809</v>
       </c>
       <c r="B23" t="n">
         <v>79020</v>
@@ -2983,17 +2983,17 @@
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Harabacken, Dlr</t>
+          <t>Harabacken, Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>478109</v>
+        <v>478062</v>
       </c>
       <c r="R23" t="n">
-        <v>6820979</v>
+        <v>6821226</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3022,7 +3022,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3032,7 +3032,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3047,22 +3047,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens, Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127443809</v>
+        <v>127443315</v>
       </c>
       <c r="B24" t="n">
-        <v>79052</v>
+        <v>79020</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3070,37 +3070,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Harabacken, Harabacken, Dlr</t>
+          <t>Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>478054</v>
+        <v>478109</v>
       </c>
       <c r="R24" t="n">
-        <v>6821168</v>
+        <v>6820979</v>
       </c>
       <c r="S24" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3139,7 +3139,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3154,12 +3154,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -3271,7 +3271,7 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Peter Turander, Håkan Thenander, Bo karlstens, Birgitta Kvist, Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3602,7 +3602,7 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Peter Turander, Håkan Thenander, Bo karlstens, Birgitta Kvist, Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -3715,10 +3715,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127441057</v>
+        <v>127443983</v>
       </c>
       <c r="B30" t="n">
-        <v>57660</v>
+        <v>91332</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3726,42 +3726,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Harabacken, Dlr</t>
+          <t>Kuusikallio, Kuusikallio, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>478319</v>
+        <v>478068</v>
       </c>
       <c r="R30" t="n">
-        <v>6820790</v>
+        <v>6821169</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3790,7 +3785,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3800,7 +3795,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3815,12 +3810,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -3934,10 +3929,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127443983</v>
+        <v>127441057</v>
       </c>
       <c r="B32" t="n">
-        <v>91332</v>
+        <v>57660</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3945,37 +3940,42 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Kuusikallio, Kuusikallio, Dlr</t>
+          <t>Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>478068</v>
+        <v>478319</v>
       </c>
       <c r="R32" t="n">
-        <v>6821169</v>
+        <v>6820790</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4004,7 +4004,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4014,7 +4014,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4029,12 +4029,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -5029,10 +5029,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127444496</v>
+        <v>127443466</v>
       </c>
       <c r="B42" t="n">
-        <v>75144</v>
+        <v>79020</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5040,21 +5040,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5064,10 +5064,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>478229</v>
+        <v>478105</v>
       </c>
       <c r="R42" t="n">
-        <v>6821051</v>
+        <v>6820956</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5136,10 +5136,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127443466</v>
+        <v>127444496</v>
       </c>
       <c r="B43" t="n">
-        <v>79020</v>
+        <v>75144</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5147,21 +5147,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5171,10 +5171,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>478105</v>
+        <v>478229</v>
       </c>
       <c r="R43" t="n">
-        <v>6820956</v>
+        <v>6821051</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5355,10 +5355,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127445040</v>
+        <v>127443816</v>
       </c>
       <c r="B45" t="n">
-        <v>79020</v>
+        <v>79052</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5366,21 +5366,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5390,13 +5390,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>478072</v>
+        <v>478071</v>
       </c>
       <c r="R45" t="n">
-        <v>6821204</v>
+        <v>6821147</v>
       </c>
       <c r="S45" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5435,12 +5435,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:22</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>På tall</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5455,22 +5450,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127444469</v>
+        <v>127443715</v>
       </c>
       <c r="B46" t="n">
-        <v>79020</v>
+        <v>79052</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5478,34 +5473,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Harabacken, Harabacken, Dlr</t>
+          <t>Kuusikallio, Kuusikallio, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>478048</v>
+        <v>478069</v>
       </c>
       <c r="R46" t="n">
-        <v>6821183</v>
+        <v>6821132</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5537,7 +5532,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5547,7 +5542,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5686,10 +5681,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127443816</v>
+        <v>127444469</v>
       </c>
       <c r="B48" t="n">
-        <v>79052</v>
+        <v>79020</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5697,21 +5692,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5721,10 +5716,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>478071</v>
+        <v>478048</v>
       </c>
       <c r="R48" t="n">
-        <v>6821147</v>
+        <v>6821183</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5793,10 +5788,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127443715</v>
+        <v>127445040</v>
       </c>
       <c r="B49" t="n">
-        <v>79052</v>
+        <v>79020</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5804,37 +5799,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Kuusikallio, Kuusikallio, Dlr</t>
+          <t>Harabacken, Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>478069</v>
+        <v>478072</v>
       </c>
       <c r="R49" t="n">
-        <v>6821132</v>
+        <v>6821204</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5863,7 +5858,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5873,7 +5868,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5888,12 +5888,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>

--- a/artfynd/A 33533-2025 artfynd.xlsx
+++ b/artfynd/A 33533-2025 artfynd.xlsx
@@ -1872,32 +1872,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127444817</v>
+        <v>127443080</v>
       </c>
       <c r="B13" t="n">
-        <v>79052</v>
+        <v>98367</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>185</v>
+        <v>219790</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1907,13 +1907,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>478071</v>
+        <v>478309</v>
       </c>
       <c r="R13" t="n">
-        <v>6821227</v>
+        <v>6820751</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1952,12 +1952,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:22</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>På gran</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1972,44 +1967,44 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127443080</v>
+        <v>127444817</v>
       </c>
       <c r="B14" t="n">
-        <v>98367</v>
+        <v>79052</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219790</v>
+        <v>185</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2019,13 +2014,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>478309</v>
+        <v>478071</v>
       </c>
       <c r="R14" t="n">
-        <v>6820751</v>
+        <v>6821227</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2054,7 +2049,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2064,7 +2059,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2079,12 +2079,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2524,10 +2524,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127442676</v>
+        <v>127444686</v>
       </c>
       <c r="B19" t="n">
-        <v>79020</v>
+        <v>79052</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2535,21 +2535,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2559,10 +2559,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>478059</v>
+        <v>478062</v>
       </c>
       <c r="R19" t="n">
-        <v>6820931</v>
+        <v>6821226</v>
       </c>
       <c r="S19" t="n">
         <v>9</v>
@@ -2594,7 +2594,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2619,19 +2619,19 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Bo karlstens, Birgitta Kvist, Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127444686</v>
+        <v>127444556</v>
       </c>
       <c r="B20" t="n">
         <v>79052</v>
@@ -2666,10 +2666,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>478062</v>
+        <v>478030</v>
       </c>
       <c r="R20" t="n">
-        <v>6821226</v>
+        <v>6821197</v>
       </c>
       <c r="S20" t="n">
         <v>9</v>
@@ -2701,7 +2701,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2711,7 +2711,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2731,17 +2731,17 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
+          <t>Peter Turander, Håkan Thenander, Bo karlstens, Birgitta Kvist, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127444556</v>
+        <v>127442676</v>
       </c>
       <c r="B21" t="n">
-        <v>79052</v>
+        <v>79020</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2749,21 +2749,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2773,10 +2773,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>478030</v>
+        <v>478059</v>
       </c>
       <c r="R21" t="n">
-        <v>6821197</v>
+        <v>6820931</v>
       </c>
       <c r="S21" t="n">
         <v>9</v>
@@ -2808,7 +2808,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2818,7 +2818,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2833,22 +2833,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Peter Turander, Håkan Thenander, Bo karlstens, Birgitta Kvist, Bengt Oldhammer</t>
+          <t>Bo karlstens, Birgitta Kvist, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127443809</v>
+        <v>127444809</v>
       </c>
       <c r="B22" t="n">
-        <v>79052</v>
+        <v>79020</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2856,21 +2856,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2880,13 +2880,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>478054</v>
+        <v>478062</v>
       </c>
       <c r="R22" t="n">
-        <v>6821168</v>
+        <v>6821226</v>
       </c>
       <c r="S22" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2915,7 +2915,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2925,7 +2925,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2940,19 +2940,19 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bo karlstens, Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127444809</v>
+        <v>127443315</v>
       </c>
       <c r="B23" t="n">
         <v>79020</v>
@@ -2983,17 +2983,17 @@
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Harabacken, Harabacken, Dlr</t>
+          <t>Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>478062</v>
+        <v>478109</v>
       </c>
       <c r="R23" t="n">
-        <v>6821226</v>
+        <v>6820979</v>
       </c>
       <c r="S23" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3022,7 +3022,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3032,7 +3032,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3047,22 +3047,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Bo karlstens, Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127443315</v>
+        <v>127443809</v>
       </c>
       <c r="B24" t="n">
-        <v>79020</v>
+        <v>79052</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3070,37 +3070,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Harabacken, Dlr</t>
+          <t>Harabacken, Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>478109</v>
+        <v>478054</v>
       </c>
       <c r="R24" t="n">
-        <v>6820979</v>
+        <v>6821168</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3139,7 +3139,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3154,12 +3154,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -3390,10 +3390,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127445612</v>
+        <v>127451855</v>
       </c>
       <c r="B27" t="n">
-        <v>79020</v>
+        <v>79052</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3401,37 +3401,40 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>478265</v>
+        <v>478077</v>
       </c>
       <c r="R27" t="n">
-        <v>6821033</v>
+        <v>6820974</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3458,19 +3461,14 @@
           <t>2025-08-13</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>10:20</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-08-13</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>10:20</t>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3479,28 +3477,29 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127445678</v>
+        <v>127445612</v>
       </c>
       <c r="B28" t="n">
-        <v>57663</v>
+        <v>79020</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3508,42 +3507,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Kuusikallio, Kuusikallio, Dlr</t>
+          <t>Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>478106</v>
+        <v>478265</v>
       </c>
       <c r="R28" t="n">
-        <v>6821168</v>
+        <v>6821033</v>
       </c>
       <c r="S28" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3572,7 +3566,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3582,7 +3576,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3597,22 +3591,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127451855</v>
+        <v>127445678</v>
       </c>
       <c r="B29" t="n">
-        <v>79052</v>
+        <v>57663</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3620,40 +3614,42 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Harabacken, Dlr</t>
+          <t>Kuusikallio, Kuusikallio, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>478077</v>
+        <v>478106</v>
       </c>
       <c r="R29" t="n">
-        <v>6820974</v>
+        <v>6821168</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3680,14 +3676,19 @@
           <t>2025-08-13</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-08-13</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>På gran</t>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3696,19 +3697,18 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -5569,53 +5569,48 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127443685</v>
+        <v>127444469</v>
       </c>
       <c r="B47" t="n">
-        <v>58033</v>
+        <v>79020</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Harabacken, Dlr</t>
+          <t>Harabacken, Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>478128</v>
+        <v>478048</v>
       </c>
       <c r="R47" t="n">
-        <v>6820965</v>
+        <v>6821183</v>
       </c>
       <c r="S47" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5644,7 +5639,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5654,7 +5649,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5669,19 +5664,19 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127444469</v>
+        <v>127445040</v>
       </c>
       <c r="B48" t="n">
         <v>79020</v>
@@ -5716,13 +5711,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>478048</v>
+        <v>478072</v>
       </c>
       <c r="R48" t="n">
-        <v>6821183</v>
+        <v>6821204</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5751,7 +5746,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5761,7 +5756,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5776,60 +5776,65 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127445040</v>
+        <v>127443685</v>
       </c>
       <c r="B49" t="n">
-        <v>79020</v>
+        <v>58033</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Harabacken, Harabacken, Dlr</t>
+          <t>Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>478072</v>
+        <v>478128</v>
       </c>
       <c r="R49" t="n">
-        <v>6821204</v>
+        <v>6820965</v>
       </c>
       <c r="S49" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5858,7 +5863,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5868,12 +5873,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>12:22</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>På tall</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5888,12 +5888,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>

--- a/artfynd/A 33533-2025 artfynd.xlsx
+++ b/artfynd/A 33533-2025 artfynd.xlsx
@@ -1113,7 +1113,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127442809</v>
+        <v>127444509</v>
       </c>
       <c r="B6" t="n">
         <v>79020</v>
@@ -1144,17 +1144,17 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kuusikallio, Kuusikallio, Dlr</t>
+          <t>Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>478309</v>
+        <v>478229</v>
       </c>
       <c r="R6" t="n">
-        <v>6820751</v>
+        <v>6821051</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1208,22 +1208,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127445814</v>
+        <v>127445695</v>
       </c>
       <c r="B7" t="n">
-        <v>79020</v>
+        <v>57660</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1231,34 +1231,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Harabacken, Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>478096</v>
+        <v>478104</v>
       </c>
       <c r="R7" t="n">
-        <v>6821144</v>
+        <v>6821165</v>
       </c>
       <c r="S7" t="n">
         <v>9</v>
@@ -1327,7 +1332,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127444509</v>
+        <v>127442809</v>
       </c>
       <c r="B8" t="n">
         <v>79020</v>
@@ -1358,17 +1363,17 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Harabacken, Dlr</t>
+          <t>Kuusikallio, Kuusikallio, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>478229</v>
+        <v>478309</v>
       </c>
       <c r="R8" t="n">
-        <v>6821051</v>
+        <v>6820751</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1397,7 +1402,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1407,7 +1412,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1422,22 +1427,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127445695</v>
+        <v>127445814</v>
       </c>
       <c r="B9" t="n">
-        <v>57660</v>
+        <v>79020</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1445,39 +1450,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Harabacken, Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>478104</v>
+        <v>478096</v>
       </c>
       <c r="R9" t="n">
-        <v>6821165</v>
+        <v>6821144</v>
       </c>
       <c r="S9" t="n">
         <v>9</v>
@@ -1546,10 +1546,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127444616</v>
+        <v>127447989</v>
       </c>
       <c r="B10" t="n">
-        <v>79052</v>
+        <v>79020</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1557,34 +1557,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Harabacken, Harabacken, Dlr</t>
+          <t>Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>478034</v>
+        <v>478360</v>
       </c>
       <c r="R10" t="n">
-        <v>6821199</v>
+        <v>6820946</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1616,7 +1616,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1641,22 +1641,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Peter Turander, Håkan Thenander, Bo karlstens, Birgitta Kvist, Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127447989</v>
+        <v>127442751</v>
       </c>
       <c r="B11" t="n">
-        <v>79020</v>
+        <v>57660</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1664,34 +1664,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>478360</v>
+        <v>478022</v>
       </c>
       <c r="R11" t="n">
-        <v>6820946</v>
+        <v>6820902</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1760,10 +1765,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127442751</v>
+        <v>127444616</v>
       </c>
       <c r="B12" t="n">
-        <v>57660</v>
+        <v>79052</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1771,39 +1776,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>185</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Harabacken, Dlr</t>
+          <t>Harabacken, Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>478022</v>
+        <v>478034</v>
       </c>
       <c r="R12" t="n">
-        <v>6820902</v>
+        <v>6821199</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1860,44 +1860,44 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander, Håkan Thenander, Bo karlstens, Birgitta Kvist, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127443080</v>
+        <v>127444817</v>
       </c>
       <c r="B13" t="n">
-        <v>98367</v>
+        <v>79052</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219790</v>
+        <v>185</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1907,13 +1907,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>478309</v>
+        <v>478071</v>
       </c>
       <c r="R13" t="n">
-        <v>6820751</v>
+        <v>6821227</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1952,7 +1952,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1967,44 +1972,44 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127444817</v>
+        <v>127443080</v>
       </c>
       <c r="B14" t="n">
-        <v>79052</v>
+        <v>98367</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>185</v>
+        <v>219790</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2014,13 +2019,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>478071</v>
+        <v>478309</v>
       </c>
       <c r="R14" t="n">
-        <v>6821227</v>
+        <v>6820751</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2049,7 +2054,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2059,12 +2064,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:22</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>På gran</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2079,12 +2079,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2198,10 +2198,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127444510</v>
+        <v>127444563</v>
       </c>
       <c r="B16" t="n">
-        <v>57663</v>
+        <v>79052</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2209,39 +2209,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Harabacken, Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>478030</v>
+        <v>478024</v>
       </c>
       <c r="R16" t="n">
-        <v>6821195</v>
+        <v>6821213</v>
       </c>
       <c r="S16" t="n">
         <v>9</v>
@@ -2273,7 +2268,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2283,7 +2278,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2298,22 +2293,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Peter Turander, Håkan Thenander, Bo karlstens, Birgitta Kvist, Bengt Oldhammer</t>
+          <t>Birgitta Kvist, Bengt Oldhammer, Bo karlstens</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127444563</v>
+        <v>127444510</v>
       </c>
       <c r="B17" t="n">
-        <v>79052</v>
+        <v>57663</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2321,34 +2316,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Harabacken, Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>478024</v>
+        <v>478030</v>
       </c>
       <c r="R17" t="n">
-        <v>6821213</v>
+        <v>6821195</v>
       </c>
       <c r="S17" t="n">
         <v>9</v>
@@ -2380,7 +2380,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2390,7 +2390,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2405,12 +2405,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Birgitta Kvist, Bengt Oldhammer, Bo karlstens</t>
+          <t>Peter Turander, Håkan Thenander, Bo karlstens, Birgitta Kvist, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2524,10 +2524,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127444686</v>
+        <v>127442676</v>
       </c>
       <c r="B19" t="n">
-        <v>79052</v>
+        <v>79020</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2535,21 +2535,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2559,10 +2559,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>478062</v>
+        <v>478059</v>
       </c>
       <c r="R19" t="n">
-        <v>6821226</v>
+        <v>6820931</v>
       </c>
       <c r="S19" t="n">
         <v>9</v>
@@ -2594,7 +2594,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2619,19 +2619,19 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
+          <t>Bo karlstens, Birgitta Kvist, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127444556</v>
+        <v>127444686</v>
       </c>
       <c r="B20" t="n">
         <v>79052</v>
@@ -2666,10 +2666,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>478030</v>
+        <v>478062</v>
       </c>
       <c r="R20" t="n">
-        <v>6821197</v>
+        <v>6821226</v>
       </c>
       <c r="S20" t="n">
         <v>9</v>
@@ -2701,7 +2701,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2711,7 +2711,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2731,17 +2731,17 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Peter Turander, Håkan Thenander, Bo karlstens, Birgitta Kvist, Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127442676</v>
+        <v>127444556</v>
       </c>
       <c r="B21" t="n">
-        <v>79020</v>
+        <v>79052</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2749,21 +2749,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2773,10 +2773,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>478059</v>
+        <v>478030</v>
       </c>
       <c r="R21" t="n">
-        <v>6820931</v>
+        <v>6821197</v>
       </c>
       <c r="S21" t="n">
         <v>9</v>
@@ -2808,7 +2808,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2818,7 +2818,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2833,22 +2833,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Bo karlstens, Birgitta Kvist, Bengt Oldhammer</t>
+          <t>Peter Turander, Håkan Thenander, Bo karlstens, Birgitta Kvist, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127444809</v>
+        <v>127444600</v>
       </c>
       <c r="B22" t="n">
-        <v>79020</v>
+        <v>57660</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2856,34 +2856,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Harabacken, Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>478062</v>
+        <v>478030</v>
       </c>
       <c r="R22" t="n">
-        <v>6821226</v>
+        <v>6821197</v>
       </c>
       <c r="S22" t="n">
         <v>9</v>
@@ -2915,7 +2920,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2925,7 +2930,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2940,22 +2945,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Bo karlstens, Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Peter Turander, Håkan Thenander, Bo karlstens, Birgitta Kvist, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127443315</v>
+        <v>127443809</v>
       </c>
       <c r="B23" t="n">
-        <v>79020</v>
+        <v>79052</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2963,37 +2968,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Harabacken, Dlr</t>
+          <t>Harabacken, Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>478109</v>
+        <v>478054</v>
       </c>
       <c r="R23" t="n">
-        <v>6820979</v>
+        <v>6821168</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3022,7 +3027,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3032,7 +3037,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3047,22 +3052,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127443809</v>
+        <v>127443315</v>
       </c>
       <c r="B24" t="n">
-        <v>79052</v>
+        <v>79020</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3070,37 +3075,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Harabacken, Harabacken, Dlr</t>
+          <t>Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>478054</v>
+        <v>478109</v>
       </c>
       <c r="R24" t="n">
-        <v>6821168</v>
+        <v>6820979</v>
       </c>
       <c r="S24" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3129,7 +3134,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3139,7 +3144,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3154,22 +3159,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127443690</v>
+        <v>127444809</v>
       </c>
       <c r="B25" t="n">
-        <v>57660</v>
+        <v>79020</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3177,42 +3182,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Harabacken, Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>478071</v>
+        <v>478062</v>
       </c>
       <c r="R25" t="n">
-        <v>6821124</v>
+        <v>6821226</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3266,19 +3266,19 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
+          <t>Bo karlstens, Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127444600</v>
+        <v>127443690</v>
       </c>
       <c r="B26" t="n">
         <v>57660</v>
@@ -3318,13 +3318,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>478030</v>
+        <v>478071</v>
       </c>
       <c r="R26" t="n">
-        <v>6821197</v>
+        <v>6821124</v>
       </c>
       <c r="S26" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3353,7 +3353,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3363,7 +3363,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3383,7 +3383,7 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Peter Turander, Håkan Thenander, Bo karlstens, Birgitta Kvist, Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -4810,53 +4810,48 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127443785</v>
+        <v>127444767</v>
       </c>
       <c r="B40" t="n">
-        <v>58033</v>
+        <v>79020</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>478207</v>
+        <v>478245</v>
       </c>
       <c r="R40" t="n">
-        <v>6821016</v>
+        <v>6821068</v>
       </c>
       <c r="S40" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4922,48 +4917,53 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127444767</v>
+        <v>127443785</v>
       </c>
       <c r="B41" t="n">
-        <v>79020</v>
+        <v>58033</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>478245</v>
+        <v>478207</v>
       </c>
       <c r="R41" t="n">
-        <v>6821068</v>
+        <v>6821016</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5029,10 +5029,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127443466</v>
+        <v>127444690</v>
       </c>
       <c r="B42" t="n">
-        <v>79020</v>
+        <v>57823</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5040,37 +5040,42 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Harabacken, Dlr</t>
+          <t>Harabacken, Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>478105</v>
+        <v>478062</v>
       </c>
       <c r="R42" t="n">
-        <v>6820956</v>
+        <v>6821226</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5099,7 +5104,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5109,7 +5114,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5124,22 +5129,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127444496</v>
+        <v>127443466</v>
       </c>
       <c r="B43" t="n">
-        <v>75144</v>
+        <v>79020</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5147,21 +5152,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5171,10 +5176,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>478229</v>
+        <v>478105</v>
       </c>
       <c r="R43" t="n">
-        <v>6821051</v>
+        <v>6820956</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5243,10 +5248,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127444690</v>
+        <v>127444496</v>
       </c>
       <c r="B44" t="n">
-        <v>57823</v>
+        <v>75144</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5254,42 +5259,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>103021</v>
+        <v>6440</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Harabacken, Harabacken, Dlr</t>
+          <t>Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>478062</v>
+        <v>478229</v>
       </c>
       <c r="R44" t="n">
-        <v>6821226</v>
+        <v>6821051</v>
       </c>
       <c r="S44" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5318,7 +5318,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5328,7 +5328,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5343,22 +5343,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127443816</v>
+        <v>127444469</v>
       </c>
       <c r="B45" t="n">
-        <v>79052</v>
+        <v>79020</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5366,21 +5366,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5390,10 +5390,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>478071</v>
+        <v>478048</v>
       </c>
       <c r="R45" t="n">
-        <v>6821147</v>
+        <v>6821183</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5462,10 +5462,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127443715</v>
+        <v>127445040</v>
       </c>
       <c r="B46" t="n">
-        <v>79052</v>
+        <v>79020</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5473,37 +5473,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Kuusikallio, Kuusikallio, Dlr</t>
+          <t>Harabacken, Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>478069</v>
+        <v>478072</v>
       </c>
       <c r="R46" t="n">
-        <v>6821132</v>
+        <v>6821204</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5532,7 +5532,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5542,7 +5542,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5557,60 +5562,65 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127444469</v>
+        <v>127443685</v>
       </c>
       <c r="B47" t="n">
-        <v>79020</v>
+        <v>58033</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Harabacken, Harabacken, Dlr</t>
+          <t>Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>478048</v>
+        <v>478128</v>
       </c>
       <c r="R47" t="n">
-        <v>6821183</v>
+        <v>6820965</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5639,7 +5649,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5649,7 +5659,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5664,22 +5674,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127445040</v>
+        <v>127443816</v>
       </c>
       <c r="B48" t="n">
-        <v>79020</v>
+        <v>79052</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5687,21 +5697,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5711,13 +5721,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>478072</v>
+        <v>478071</v>
       </c>
       <c r="R48" t="n">
-        <v>6821204</v>
+        <v>6821147</v>
       </c>
       <c r="S48" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5746,7 +5756,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5756,12 +5766,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:22</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>På tall</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5776,65 +5781,60 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127443685</v>
+        <v>127443715</v>
       </c>
       <c r="B49" t="n">
-        <v>58033</v>
+        <v>79052</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>103015</v>
+        <v>185</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Harabacken, Dlr</t>
+          <t>Kuusikallio, Kuusikallio, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>478128</v>
+        <v>478069</v>
       </c>
       <c r="R49" t="n">
-        <v>6820965</v>
+        <v>6821132</v>
       </c>
       <c r="S49" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5863,7 +5863,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5873,7 +5873,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5888,22 +5888,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127443980</v>
+        <v>127444902</v>
       </c>
       <c r="B50" t="n">
-        <v>79020</v>
+        <v>79052</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5911,37 +5911,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Harabacken, Dlr</t>
+          <t>Harabacken, Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>478207</v>
+        <v>478072</v>
       </c>
       <c r="R50" t="n">
-        <v>6821016</v>
+        <v>6821204</v>
       </c>
       <c r="S50" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5970,7 +5970,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5980,7 +5980,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5995,22 +6000,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127444902</v>
+        <v>127443980</v>
       </c>
       <c r="B51" t="n">
-        <v>79052</v>
+        <v>79020</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6018,37 +6023,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Harabacken, Harabacken, Dlr</t>
+          <t>Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>478072</v>
+        <v>478207</v>
       </c>
       <c r="R51" t="n">
-        <v>6821204</v>
+        <v>6821016</v>
       </c>
       <c r="S51" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6077,7 +6082,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6087,12 +6092,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:22</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>På gran</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6107,12 +6107,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>

--- a/artfynd/A 33533-2025 artfynd.xlsx
+++ b/artfynd/A 33533-2025 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127443978</v>
+        <v>127445652</v>
       </c>
       <c r="B3" t="n">
-        <v>75144</v>
+        <v>79020</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>478207</v>
+        <v>478270</v>
       </c>
       <c r="R3" t="n">
-        <v>6821016</v>
+        <v>6821004</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -863,11 +863,6 @@
       <c r="AB3" t="inlineStr">
         <is>
           <t>10:20</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Vitgrynig nållav på äldre gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,48 +889,53 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127445652</v>
+        <v>127444794</v>
       </c>
       <c r="B4" t="n">
-        <v>79020</v>
+        <v>5177</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Harabacken, Dlr</t>
+          <t>Harabacken, Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>478270</v>
+        <v>478062</v>
       </c>
       <c r="R4" t="n">
-        <v>6821004</v>
+        <v>6821226</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -964,7 +964,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -989,65 +989,60 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127444794</v>
+        <v>127443978</v>
       </c>
       <c r="B5" t="n">
-        <v>5177</v>
+        <v>75144</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100526</v>
+        <v>6440</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Harabacken, Harabacken, Dlr</t>
+          <t>Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>478062</v>
+        <v>478207</v>
       </c>
       <c r="R5" t="n">
-        <v>6821226</v>
+        <v>6821016</v>
       </c>
       <c r="S5" t="n">
-        <v>9</v>
+        <v>50</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1076,7 +1071,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1086,7 +1081,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav på äldre gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1101,22 +1101,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127444509</v>
+        <v>127445695</v>
       </c>
       <c r="B6" t="n">
-        <v>79020</v>
+        <v>57660</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1124,37 +1124,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Harabacken, Dlr</t>
+          <t>Harabacken, Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>478229</v>
+        <v>478104</v>
       </c>
       <c r="R6" t="n">
-        <v>6821051</v>
+        <v>6821165</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1183,7 +1188,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1193,7 +1198,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1208,22 +1213,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127445695</v>
+        <v>127442809</v>
       </c>
       <c r="B7" t="n">
-        <v>57660</v>
+        <v>79020</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1231,42 +1236,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Harabacken, Harabacken, Dlr</t>
+          <t>Kuusikallio, Kuusikallio, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>478104</v>
+        <v>478309</v>
       </c>
       <c r="R7" t="n">
-        <v>6821165</v>
+        <v>6820751</v>
       </c>
       <c r="S7" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1305,7 +1305,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1332,7 +1332,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127442809</v>
+        <v>127445814</v>
       </c>
       <c r="B8" t="n">
         <v>79020</v>
@@ -1363,17 +1363,17 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kuusikallio, Kuusikallio, Dlr</t>
+          <t>Harabacken, Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>478309</v>
+        <v>478096</v>
       </c>
       <c r="R8" t="n">
-        <v>6820751</v>
+        <v>6821144</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1402,7 +1402,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1412,7 +1412,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1439,7 +1439,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127445814</v>
+        <v>127444509</v>
       </c>
       <c r="B9" t="n">
         <v>79020</v>
@@ -1470,17 +1470,17 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Harabacken, Harabacken, Dlr</t>
+          <t>Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>478096</v>
+        <v>478229</v>
       </c>
       <c r="R9" t="n">
-        <v>6821144</v>
+        <v>6821051</v>
       </c>
       <c r="S9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1519,7 +1519,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1534,22 +1534,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127447989</v>
+        <v>127444616</v>
       </c>
       <c r="B10" t="n">
-        <v>79020</v>
+        <v>79052</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1557,34 +1557,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Harabacken, Dlr</t>
+          <t>Harabacken, Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>478360</v>
+        <v>478034</v>
       </c>
       <c r="R10" t="n">
-        <v>6820946</v>
+        <v>6821199</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1616,7 +1616,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1641,12 +1641,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1765,10 +1765,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127444616</v>
+        <v>127447989</v>
       </c>
       <c r="B12" t="n">
-        <v>79052</v>
+        <v>79020</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1776,34 +1776,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Harabacken, Harabacken, Dlr</t>
+          <t>Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>478034</v>
+        <v>478360</v>
       </c>
       <c r="R12" t="n">
-        <v>6821199</v>
+        <v>6820946</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1860,12 +1860,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Peter Turander, Håkan Thenander, Bo karlstens, Birgitta Kvist, Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1987,7 +1987,7 @@
         <v>127443080</v>
       </c>
       <c r="B14" t="n">
-        <v>98367</v>
+        <v>98373</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Birgitta Kvist, Bengt Oldhammer, Bo karlstens</t>
+          <t>Bo karlstens, Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2410,7 +2410,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Peter Turander, Håkan Thenander, Bo karlstens, Birgitta Kvist, Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2517,17 +2517,17 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
+          <t>Peter Turander, Håkan Thenander, Bo karlstens, Birgitta Kvist, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127442676</v>
+        <v>127444686</v>
       </c>
       <c r="B19" t="n">
-        <v>79020</v>
+        <v>79052</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2535,21 +2535,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2559,10 +2559,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>478059</v>
+        <v>478062</v>
       </c>
       <c r="R19" t="n">
-        <v>6820931</v>
+        <v>6821226</v>
       </c>
       <c r="S19" t="n">
         <v>9</v>
@@ -2594,7 +2594,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2619,19 +2619,19 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Bo karlstens, Birgitta Kvist, Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127444686</v>
+        <v>127444556</v>
       </c>
       <c r="B20" t="n">
         <v>79052</v>
@@ -2666,10 +2666,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>478062</v>
+        <v>478030</v>
       </c>
       <c r="R20" t="n">
-        <v>6821226</v>
+        <v>6821197</v>
       </c>
       <c r="S20" t="n">
         <v>9</v>
@@ -2701,7 +2701,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2711,7 +2711,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2738,10 +2738,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127444556</v>
+        <v>127442676</v>
       </c>
       <c r="B21" t="n">
-        <v>79052</v>
+        <v>79020</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2749,21 +2749,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2773,10 +2773,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>478030</v>
+        <v>478059</v>
       </c>
       <c r="R21" t="n">
-        <v>6821197</v>
+        <v>6820931</v>
       </c>
       <c r="S21" t="n">
         <v>9</v>
@@ -2808,7 +2808,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2818,7 +2818,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2833,22 +2833,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Peter Turander, Håkan Thenander, Bo karlstens, Birgitta Kvist, Bengt Oldhammer</t>
+          <t>Bo karlstens, Birgitta Kvist, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127444600</v>
+        <v>127443809</v>
       </c>
       <c r="B22" t="n">
-        <v>57660</v>
+        <v>79052</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2856,42 +2856,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>185</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Harabacken, Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>478030</v>
+        <v>478054</v>
       </c>
       <c r="R22" t="n">
-        <v>6821197</v>
+        <v>6821168</v>
       </c>
       <c r="S22" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2920,7 +2915,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2930,7 +2925,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2945,22 +2940,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Peter Turander, Håkan Thenander, Bo karlstens, Birgitta Kvist, Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127443809</v>
+        <v>127443690</v>
       </c>
       <c r="B23" t="n">
-        <v>79052</v>
+        <v>57660</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2968,37 +2963,42 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>185</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Harabacken, Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>478054</v>
+        <v>478071</v>
       </c>
       <c r="R23" t="n">
-        <v>6821168</v>
+        <v>6821124</v>
       </c>
       <c r="S23" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3027,7 +3027,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3037,7 +3037,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3052,22 +3052,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127443315</v>
+        <v>127444600</v>
       </c>
       <c r="B24" t="n">
-        <v>79020</v>
+        <v>57660</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3075,37 +3075,42 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Harabacken, Dlr</t>
+          <t>Harabacken, Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>478109</v>
+        <v>478030</v>
       </c>
       <c r="R24" t="n">
-        <v>6820979</v>
+        <v>6821197</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3134,7 +3139,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3144,7 +3149,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3159,12 +3164,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -3278,10 +3283,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127443690</v>
+        <v>127443315</v>
       </c>
       <c r="B26" t="n">
-        <v>57660</v>
+        <v>79020</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3289,42 +3294,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Harabacken, Harabacken, Dlr</t>
+          <t>Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>478071</v>
+        <v>478109</v>
       </c>
       <c r="R26" t="n">
-        <v>6821124</v>
+        <v>6820979</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3353,7 +3353,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3363,7 +3363,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3378,22 +3378,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127451855</v>
+        <v>127445612</v>
       </c>
       <c r="B27" t="n">
-        <v>79052</v>
+        <v>79020</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3401,40 +3401,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>478077</v>
+        <v>478265</v>
       </c>
       <c r="R27" t="n">
-        <v>6820974</v>
+        <v>6821033</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3461,14 +3458,19 @@
           <t>2025-08-13</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-08-13</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>På gran</t>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3477,29 +3479,28 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127445612</v>
+        <v>127451855</v>
       </c>
       <c r="B28" t="n">
-        <v>79020</v>
+        <v>79052</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3507,37 +3508,40 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>478265</v>
+        <v>478077</v>
       </c>
       <c r="R28" t="n">
-        <v>6821033</v>
+        <v>6820974</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3564,19 +3568,14 @@
           <t>2025-08-13</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>10:20</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-08-13</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>10:20</t>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3585,18 +3584,19 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -3718,7 +3718,7 @@
         <v>127443983</v>
       </c>
       <c r="B30" t="n">
-        <v>91332</v>
+        <v>91338</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3822,10 +3822,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127445756</v>
+        <v>127441057</v>
       </c>
       <c r="B31" t="n">
-        <v>79020</v>
+        <v>57660</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3833,37 +3833,42 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Harabacken, Harabacken, Dlr</t>
+          <t>Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>478104</v>
+        <v>478319</v>
       </c>
       <c r="R31" t="n">
-        <v>6821165</v>
+        <v>6820790</v>
       </c>
       <c r="S31" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3892,7 +3897,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3902,7 +3907,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3917,22 +3922,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127441057</v>
+        <v>127445756</v>
       </c>
       <c r="B32" t="n">
-        <v>57660</v>
+        <v>79020</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3940,42 +3945,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Harabacken, Dlr</t>
+          <t>Harabacken, Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>478319</v>
+        <v>478104</v>
       </c>
       <c r="R32" t="n">
-        <v>6820790</v>
+        <v>6821165</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4004,7 +4004,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4014,7 +4014,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4029,12 +4029,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -4584,7 +4584,7 @@
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
+          <t>Peter Turander, Håkan Thenander, Bo karlstens, Birgitta Kvist, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
@@ -5355,10 +5355,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127444469</v>
+        <v>127443816</v>
       </c>
       <c r="B45" t="n">
-        <v>79020</v>
+        <v>79052</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5366,21 +5366,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5390,10 +5390,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>478048</v>
+        <v>478071</v>
       </c>
       <c r="R45" t="n">
-        <v>6821183</v>
+        <v>6821147</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5455,17 +5455,17 @@
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
+          <t>Peter Turander, Håkan Thenander, Bo karlstens, Birgitta Kvist, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127445040</v>
+        <v>127443715</v>
       </c>
       <c r="B46" t="n">
-        <v>79020</v>
+        <v>79052</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5473,37 +5473,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Harabacken, Harabacken, Dlr</t>
+          <t>Kuusikallio, Kuusikallio, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>478072</v>
+        <v>478069</v>
       </c>
       <c r="R46" t="n">
-        <v>6821204</v>
+        <v>6821132</v>
       </c>
       <c r="S46" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5532,7 +5532,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5542,12 +5542,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:22</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>På tall</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5562,12 +5557,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -5686,10 +5681,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127443816</v>
+        <v>127444469</v>
       </c>
       <c r="B48" t="n">
-        <v>79052</v>
+        <v>79020</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5697,21 +5692,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5721,10 +5716,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>478071</v>
+        <v>478048</v>
       </c>
       <c r="R48" t="n">
-        <v>6821147</v>
+        <v>6821183</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5793,10 +5788,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127443715</v>
+        <v>127445040</v>
       </c>
       <c r="B49" t="n">
-        <v>79052</v>
+        <v>79020</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5804,37 +5799,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Kuusikallio, Kuusikallio, Dlr</t>
+          <t>Harabacken, Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>478069</v>
+        <v>478072</v>
       </c>
       <c r="R49" t="n">
-        <v>6821132</v>
+        <v>6821204</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5863,7 +5858,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5873,7 +5868,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5888,12 +5888,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>

--- a/artfynd/A 33533-2025 artfynd.xlsx
+++ b/artfynd/A 33533-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127445512</v>
       </c>
       <c r="B2" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127445652</v>
+        <v>127443978</v>
       </c>
       <c r="B3" t="n">
-        <v>79020</v>
+        <v>75147</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>478270</v>
+        <v>478207</v>
       </c>
       <c r="R3" t="n">
-        <v>6821004</v>
+        <v>6821016</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -863,6 +863,11 @@
       <c r="AB3" t="inlineStr">
         <is>
           <t>10:20</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav på äldre gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,53 +894,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127444794</v>
+        <v>127445652</v>
       </c>
       <c r="B4" t="n">
-        <v>5177</v>
+        <v>79023</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Harabacken, Harabacken, Dlr</t>
+          <t>Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>478062</v>
+        <v>478270</v>
       </c>
       <c r="R4" t="n">
-        <v>6821226</v>
+        <v>6821004</v>
       </c>
       <c r="S4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -964,7 +964,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -989,60 +989,65 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127443978</v>
+        <v>127444794</v>
       </c>
       <c r="B5" t="n">
-        <v>75144</v>
+        <v>5177</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6440</v>
+        <v>100526</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Harabacken, Dlr</t>
+          <t>Harabacken, Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>478207</v>
+        <v>478062</v>
       </c>
       <c r="R5" t="n">
-        <v>6821016</v>
+        <v>6821226</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1071,7 +1076,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1081,12 +1086,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:20</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Vitgrynig nållav på äldre gran</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1101,22 +1101,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127445695</v>
+        <v>127442809</v>
       </c>
       <c r="B6" t="n">
-        <v>57660</v>
+        <v>79023</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1124,42 +1124,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Harabacken, Harabacken, Dlr</t>
+          <t>Kuusikallio, Kuusikallio, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>478104</v>
+        <v>478309</v>
       </c>
       <c r="R6" t="n">
-        <v>6821165</v>
+        <v>6820751</v>
       </c>
       <c r="S6" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1188,7 +1183,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1198,7 +1193,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1225,10 +1220,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127442809</v>
+        <v>127445814</v>
       </c>
       <c r="B7" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1256,17 +1251,17 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kuusikallio, Kuusikallio, Dlr</t>
+          <t>Harabacken, Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>478309</v>
+        <v>478096</v>
       </c>
       <c r="R7" t="n">
-        <v>6820751</v>
+        <v>6821144</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1295,7 +1290,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1305,7 +1300,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1332,10 +1327,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127445814</v>
+        <v>127444509</v>
       </c>
       <c r="B8" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1363,17 +1358,17 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Harabacken, Harabacken, Dlr</t>
+          <t>Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>478096</v>
+        <v>478229</v>
       </c>
       <c r="R8" t="n">
-        <v>6821144</v>
+        <v>6821051</v>
       </c>
       <c r="S8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1402,7 +1397,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1412,7 +1407,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1427,22 +1422,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127444509</v>
+        <v>127445695</v>
       </c>
       <c r="B9" t="n">
-        <v>79020</v>
+        <v>57663</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1450,37 +1445,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Harabacken, Dlr</t>
+          <t>Harabacken, Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>478229</v>
+        <v>478104</v>
       </c>
       <c r="R9" t="n">
-        <v>6821051</v>
+        <v>6821165</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1519,7 +1519,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1534,12 +1534,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1549,7 +1549,7 @@
         <v>127444616</v>
       </c>
       <c r="B10" t="n">
-        <v>79052</v>
+        <v>79055</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1653,10 +1653,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127442751</v>
+        <v>127447989</v>
       </c>
       <c r="B11" t="n">
-        <v>57660</v>
+        <v>79023</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1664,39 +1664,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>478022</v>
+        <v>478360</v>
       </c>
       <c r="R11" t="n">
-        <v>6820902</v>
+        <v>6820946</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1765,10 +1760,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127447989</v>
+        <v>127442751</v>
       </c>
       <c r="B12" t="n">
-        <v>79020</v>
+        <v>57663</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1776,34 +1771,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>478360</v>
+        <v>478022</v>
       </c>
       <c r="R12" t="n">
-        <v>6820946</v>
+        <v>6820902</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1872,32 +1872,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127444817</v>
+        <v>127443080</v>
       </c>
       <c r="B13" t="n">
-        <v>79052</v>
+        <v>98376</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>185</v>
+        <v>219790</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1907,13 +1907,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>478071</v>
+        <v>478309</v>
       </c>
       <c r="R13" t="n">
-        <v>6821227</v>
+        <v>6820751</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1952,12 +1952,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:22</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>På gran</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1972,44 +1967,44 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127443080</v>
+        <v>127444817</v>
       </c>
       <c r="B14" t="n">
-        <v>98373</v>
+        <v>79055</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219790</v>
+        <v>185</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2019,13 +2014,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>478309</v>
+        <v>478071</v>
       </c>
       <c r="R14" t="n">
-        <v>6820751</v>
+        <v>6821227</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2054,7 +2049,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2064,7 +2059,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2079,12 +2079,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2094,7 +2094,7 @@
         <v>127444484</v>
       </c>
       <c r="B15" t="n">
-        <v>79052</v>
+        <v>79055</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2191,7 +2191,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
+          <t>Peter Turander, Håkan Thenander, Bo karlstens, Birgitta Kvist, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2201,7 +2201,7 @@
         <v>127444563</v>
       </c>
       <c r="B16" t="n">
-        <v>79052</v>
+        <v>79055</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2308,7 +2308,7 @@
         <v>127444510</v>
       </c>
       <c r="B17" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2410,7 +2410,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
+          <t>Peter Turander, Håkan Thenander, Bo karlstens, Birgitta Kvist, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2517,7 +2517,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Peter Turander, Håkan Thenander, Bo karlstens, Birgitta Kvist, Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2527,7 +2527,7 @@
         <v>127444686</v>
       </c>
       <c r="B19" t="n">
-        <v>79052</v>
+        <v>79055</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2634,7 +2634,7 @@
         <v>127444556</v>
       </c>
       <c r="B20" t="n">
-        <v>79052</v>
+        <v>79055</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2741,7 +2741,7 @@
         <v>127442676</v>
       </c>
       <c r="B21" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2848,7 +2848,7 @@
         <v>127443809</v>
       </c>
       <c r="B22" t="n">
-        <v>79052</v>
+        <v>79055</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2952,10 +2952,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127443690</v>
+        <v>127444809</v>
       </c>
       <c r="B23" t="n">
-        <v>57660</v>
+        <v>79023</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2963,42 +2963,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Harabacken, Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>478071</v>
+        <v>478062</v>
       </c>
       <c r="R23" t="n">
-        <v>6821124</v>
+        <v>6821226</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3027,7 +3022,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3037,7 +3032,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3052,22 +3047,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
+          <t>Bo karlstens, Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127444600</v>
+        <v>127443315</v>
       </c>
       <c r="B24" t="n">
-        <v>57660</v>
+        <v>79023</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3075,42 +3070,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Harabacken, Harabacken, Dlr</t>
+          <t>Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>478030</v>
+        <v>478109</v>
       </c>
       <c r="R24" t="n">
-        <v>6821197</v>
+        <v>6820979</v>
       </c>
       <c r="S24" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3139,7 +3129,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3149,7 +3139,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3164,22 +3154,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127444809</v>
+        <v>127443690</v>
       </c>
       <c r="B25" t="n">
-        <v>79020</v>
+        <v>57663</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3187,37 +3177,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Harabacken, Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>478062</v>
+        <v>478071</v>
       </c>
       <c r="R25" t="n">
-        <v>6821226</v>
+        <v>6821124</v>
       </c>
       <c r="S25" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3246,7 +3241,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3256,7 +3251,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3271,22 +3266,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Bo karlstens, Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127443315</v>
+        <v>127444600</v>
       </c>
       <c r="B26" t="n">
-        <v>79020</v>
+        <v>57663</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3294,37 +3289,42 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Harabacken, Dlr</t>
+          <t>Harabacken, Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>478109</v>
+        <v>478030</v>
       </c>
       <c r="R26" t="n">
-        <v>6820979</v>
+        <v>6821197</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3353,7 +3353,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3363,7 +3363,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3378,22 +3378,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127445612</v>
+        <v>127451855</v>
       </c>
       <c r="B27" t="n">
-        <v>79020</v>
+        <v>79055</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3401,37 +3401,40 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>478265</v>
+        <v>478077</v>
       </c>
       <c r="R27" t="n">
-        <v>6821033</v>
+        <v>6820974</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3458,19 +3461,14 @@
           <t>2025-08-13</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>10:20</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-08-13</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>10:20</t>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3479,28 +3477,29 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127451855</v>
+        <v>127445612</v>
       </c>
       <c r="B28" t="n">
-        <v>79052</v>
+        <v>79023</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3508,40 +3507,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>478077</v>
+        <v>478265</v>
       </c>
       <c r="R28" t="n">
-        <v>6820974</v>
+        <v>6821033</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3568,14 +3564,19 @@
           <t>2025-08-13</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-08-13</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>På gran</t>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3584,19 +3585,18 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -3606,7 +3606,7 @@
         <v>127445678</v>
       </c>
       <c r="B29" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3718,7 +3718,7 @@
         <v>127443983</v>
       </c>
       <c r="B30" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3822,10 +3822,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127441057</v>
+        <v>127445756</v>
       </c>
       <c r="B31" t="n">
-        <v>57660</v>
+        <v>79023</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3833,42 +3833,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Harabacken, Dlr</t>
+          <t>Harabacken, Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>478319</v>
+        <v>478104</v>
       </c>
       <c r="R31" t="n">
-        <v>6820790</v>
+        <v>6821165</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3897,7 +3892,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3907,7 +3902,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3922,22 +3917,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127445756</v>
+        <v>127441057</v>
       </c>
       <c r="B32" t="n">
-        <v>79020</v>
+        <v>57663</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3945,37 +3940,42 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Harabacken, Harabacken, Dlr</t>
+          <t>Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>478104</v>
+        <v>478319</v>
       </c>
       <c r="R32" t="n">
-        <v>6821165</v>
+        <v>6820790</v>
       </c>
       <c r="S32" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4004,7 +4004,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4014,7 +4014,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4029,12 +4029,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -4044,7 +4044,7 @@
         <v>127444491</v>
       </c>
       <c r="B33" t="n">
-        <v>79052</v>
+        <v>79055</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4156,7 +4156,7 @@
         <v>127444374</v>
       </c>
       <c r="B34" t="n">
-        <v>79052</v>
+        <v>79055</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4263,7 +4263,7 @@
         <v>127444793</v>
       </c>
       <c r="B35" t="n">
-        <v>57823</v>
+        <v>57826</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4375,7 +4375,7 @@
         <v>127444001</v>
       </c>
       <c r="B36" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4479,10 +4479,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127443762</v>
+        <v>127445635</v>
       </c>
       <c r="B37" t="n">
-        <v>57663</v>
+        <v>79612</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4490,39 +4490,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Harabacken, Harabacken, Dlr</t>
+          <t>Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>478071</v>
+        <v>478265</v>
       </c>
       <c r="R37" t="n">
-        <v>6821147</v>
+        <v>6821019</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4554,7 +4549,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4564,7 +4559,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4579,22 +4574,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Peter Turander, Håkan Thenander, Bo karlstens, Birgitta Kvist, Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127444502</v>
+        <v>127443762</v>
       </c>
       <c r="B38" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4631,13 +4626,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>478062</v>
+        <v>478071</v>
       </c>
       <c r="R38" t="n">
-        <v>6821201</v>
+        <v>6821147</v>
       </c>
       <c r="S38" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4666,7 +4661,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4676,7 +4671,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4691,22 +4686,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127445635</v>
+        <v>127444502</v>
       </c>
       <c r="B39" t="n">
-        <v>79609</v>
+        <v>57666</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4714,37 +4709,42 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Harabacken, Dlr</t>
+          <t>Harabacken, Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>478265</v>
+        <v>478062</v>
       </c>
       <c r="R39" t="n">
-        <v>6821019</v>
+        <v>6821201</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4773,7 +4773,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4783,7 +4783,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4798,12 +4798,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -4813,7 +4813,7 @@
         <v>127444767</v>
       </c>
       <c r="B40" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4920,7 +4920,7 @@
         <v>127443785</v>
       </c>
       <c r="B41" t="n">
-        <v>58033</v>
+        <v>58036</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5029,10 +5029,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127444690</v>
+        <v>127443466</v>
       </c>
       <c r="B42" t="n">
-        <v>57823</v>
+        <v>79023</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5040,42 +5040,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Harabacken, Harabacken, Dlr</t>
+          <t>Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>478062</v>
+        <v>478105</v>
       </c>
       <c r="R42" t="n">
-        <v>6821226</v>
+        <v>6820956</v>
       </c>
       <c r="S42" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5104,7 +5099,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5114,7 +5109,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5129,22 +5124,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127443466</v>
+        <v>127444496</v>
       </c>
       <c r="B43" t="n">
-        <v>79020</v>
+        <v>75147</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5152,21 +5147,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5176,10 +5171,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>478105</v>
+        <v>478229</v>
       </c>
       <c r="R43" t="n">
-        <v>6820956</v>
+        <v>6821051</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5248,10 +5243,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127444496</v>
+        <v>127444690</v>
       </c>
       <c r="B44" t="n">
-        <v>75144</v>
+        <v>57826</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5259,37 +5254,42 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6440</v>
+        <v>103021</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Harabacken, Dlr</t>
+          <t>Harabacken, Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>478229</v>
+        <v>478062</v>
       </c>
       <c r="R44" t="n">
-        <v>6821051</v>
+        <v>6821226</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5318,7 +5318,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5328,7 +5328,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5343,22 +5343,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127443816</v>
+        <v>127445040</v>
       </c>
       <c r="B45" t="n">
-        <v>79052</v>
+        <v>79023</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5366,21 +5366,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5390,13 +5390,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>478071</v>
+        <v>478072</v>
       </c>
       <c r="R45" t="n">
-        <v>6821147</v>
+        <v>6821204</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5435,7 +5435,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5450,22 +5455,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Peter Turander, Håkan Thenander, Bo karlstens, Birgitta Kvist, Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127443715</v>
+        <v>127443816</v>
       </c>
       <c r="B46" t="n">
-        <v>79052</v>
+        <v>79055</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5493,14 +5498,14 @@
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Kuusikallio, Kuusikallio, Dlr</t>
+          <t>Harabacken, Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>478069</v>
+        <v>478071</v>
       </c>
       <c r="R46" t="n">
-        <v>6821132</v>
+        <v>6821147</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5532,7 +5537,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5542,7 +5547,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5569,53 +5574,48 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127443685</v>
+        <v>127443715</v>
       </c>
       <c r="B47" t="n">
-        <v>58033</v>
+        <v>79055</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>103015</v>
+        <v>185</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Harabacken, Dlr</t>
+          <t>Kuusikallio, Kuusikallio, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>478128</v>
+        <v>478069</v>
       </c>
       <c r="R47" t="n">
-        <v>6820965</v>
+        <v>6821132</v>
       </c>
       <c r="S47" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5644,7 +5644,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5654,7 +5654,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5669,12 +5669,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
@@ -5684,7 +5684,7 @@
         <v>127444469</v>
       </c>
       <c r="B48" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5781,55 +5781,60 @@
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
+          <t>Peter Turander, Håkan Thenander, Bo karlstens, Birgitta Kvist, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127445040</v>
+        <v>127443685</v>
       </c>
       <c r="B49" t="n">
-        <v>79020</v>
+        <v>58036</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Harabacken, Harabacken, Dlr</t>
+          <t>Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>478072</v>
+        <v>478128</v>
       </c>
       <c r="R49" t="n">
-        <v>6821204</v>
+        <v>6820965</v>
       </c>
       <c r="S49" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5858,7 +5863,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5868,12 +5873,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>12:22</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>På tall</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5888,12 +5888,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
@@ -5903,7 +5903,7 @@
         <v>127444902</v>
       </c>
       <c r="B50" t="n">
-        <v>79052</v>
+        <v>79055</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6015,7 +6015,7 @@
         <v>127443980</v>
       </c>
       <c r="B51" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6122,7 +6122,7 @@
         <v>127442782</v>
       </c>
       <c r="B52" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>

--- a/artfynd/A 33533-2025 artfynd.xlsx
+++ b/artfynd/A 33533-2025 artfynd.xlsx
@@ -675,45 +675,50 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127445512</v>
+        <v>127444794</v>
       </c>
       <c r="B2" t="n">
-        <v>79023</v>
+        <v>5177</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Harabacken, Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>478104</v>
+        <v>478062</v>
       </c>
       <c r="R2" t="n">
-        <v>6821179</v>
+        <v>6821226</v>
       </c>
       <c r="S2" t="n">
         <v>9</v>
@@ -745,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,7 +780,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Bo karlstens, Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -785,7 +790,7 @@
         <v>127443978</v>
       </c>
       <c r="B3" t="n">
-        <v>75147</v>
+        <v>75153</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +902,7 @@
         <v>127445652</v>
       </c>
       <c r="B4" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,50 +1006,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127444794</v>
+        <v>127445512</v>
       </c>
       <c r="B5" t="n">
-        <v>5177</v>
+        <v>79029</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Harabacken, Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>478062</v>
+        <v>478104</v>
       </c>
       <c r="R5" t="n">
-        <v>6821226</v>
+        <v>6821179</v>
       </c>
       <c r="S5" t="n">
         <v>9</v>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1106,17 +1106,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bo karlstens, Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127442809</v>
+        <v>127445695</v>
       </c>
       <c r="B6" t="n">
-        <v>79023</v>
+        <v>57669</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1124,37 +1124,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kuusikallio, Kuusikallio, Dlr</t>
+          <t>Harabacken, Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>478309</v>
+        <v>478104</v>
       </c>
       <c r="R6" t="n">
-        <v>6820751</v>
+        <v>6821165</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1183,7 +1188,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1193,7 +1198,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1220,10 +1225,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127445814</v>
+        <v>127442809</v>
       </c>
       <c r="B7" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1251,17 +1256,17 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Harabacken, Harabacken, Dlr</t>
+          <t>Kuusikallio, Kuusikallio, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>478096</v>
+        <v>478309</v>
       </c>
       <c r="R7" t="n">
-        <v>6821144</v>
+        <v>6820751</v>
       </c>
       <c r="S7" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1290,7 +1295,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1300,7 +1305,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1327,10 +1332,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127444509</v>
+        <v>127445814</v>
       </c>
       <c r="B8" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1358,17 +1363,17 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Harabacken, Dlr</t>
+          <t>Harabacken, Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>478229</v>
+        <v>478096</v>
       </c>
       <c r="R8" t="n">
-        <v>6821051</v>
+        <v>6821144</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1397,7 +1402,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1407,7 +1412,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1422,22 +1427,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127445695</v>
+        <v>127444509</v>
       </c>
       <c r="B9" t="n">
-        <v>57663</v>
+        <v>79029</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1445,42 +1450,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Harabacken, Harabacken, Dlr</t>
+          <t>Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>478104</v>
+        <v>478229</v>
       </c>
       <c r="R9" t="n">
-        <v>6821165</v>
+        <v>6821051</v>
       </c>
       <c r="S9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1519,7 +1519,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1534,22 +1534,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127444616</v>
+        <v>127442751</v>
       </c>
       <c r="B10" t="n">
-        <v>79055</v>
+        <v>57669</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1557,34 +1557,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>185</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Harabacken, Harabacken, Dlr</t>
+          <t>Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>478034</v>
+        <v>478022</v>
       </c>
       <c r="R10" t="n">
-        <v>6821199</v>
+        <v>6820902</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1616,7 +1621,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1626,7 +1631,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1641,22 +1646,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127447989</v>
+        <v>127444616</v>
       </c>
       <c r="B11" t="n">
-        <v>79023</v>
+        <v>79061</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1664,34 +1669,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Harabacken, Dlr</t>
+          <t>Harabacken, Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>478360</v>
+        <v>478034</v>
       </c>
       <c r="R11" t="n">
-        <v>6820946</v>
+        <v>6821199</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1723,7 +1728,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1733,7 +1738,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1748,22 +1753,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander, Håkan Thenander, Bo karlstens, Birgitta Kvist, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127442751</v>
+        <v>127447989</v>
       </c>
       <c r="B12" t="n">
-        <v>57663</v>
+        <v>79029</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1771,39 +1776,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>478022</v>
+        <v>478360</v>
       </c>
       <c r="R12" t="n">
-        <v>6820902</v>
+        <v>6820946</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1875,7 +1875,7 @@
         <v>127443080</v>
       </c>
       <c r="B13" t="n">
-        <v>98376</v>
+        <v>98384</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
+          <t>Peter Turander, Håkan Thenander, Bo karlstens, Birgitta Kvist, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -1982,7 +1982,7 @@
         <v>127444817</v>
       </c>
       <c r="B14" t="n">
-        <v>79055</v>
+        <v>79061</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         <v>127444484</v>
       </c>
       <c r="B15" t="n">
-        <v>79055</v>
+        <v>79061</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2191,7 +2191,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Peter Turander, Håkan Thenander, Bo karlstens, Birgitta Kvist, Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2201,7 +2201,7 @@
         <v>127444563</v>
       </c>
       <c r="B16" t="n">
-        <v>79055</v>
+        <v>79061</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Bo karlstens, Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Birgitta Kvist, Bengt Oldhammer, Bo karlstens</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2308,7 +2308,7 @@
         <v>127444510</v>
       </c>
       <c r="B17" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
         <v>127444686</v>
       </c>
       <c r="B19" t="n">
-        <v>79055</v>
+        <v>79061</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2634,7 +2634,7 @@
         <v>127444556</v>
       </c>
       <c r="B20" t="n">
-        <v>79055</v>
+        <v>79061</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
+          <t>Peter Turander, Håkan Thenander, Bo karlstens, Birgitta Kvist, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2741,7 +2741,7 @@
         <v>127442676</v>
       </c>
       <c r="B21" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2848,7 +2848,7 @@
         <v>127443809</v>
       </c>
       <c r="B22" t="n">
-        <v>79055</v>
+        <v>79061</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2955,7 +2955,7 @@
         <v>127444809</v>
       </c>
       <c r="B23" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3059,10 +3059,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127443315</v>
+        <v>127443690</v>
       </c>
       <c r="B24" t="n">
-        <v>79023</v>
+        <v>57669</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3070,37 +3070,42 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Harabacken, Dlr</t>
+          <t>Harabacken, Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>478109</v>
+        <v>478071</v>
       </c>
       <c r="R24" t="n">
-        <v>6820979</v>
+        <v>6821124</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3129,7 +3134,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3139,7 +3144,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3154,22 +3159,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127443690</v>
+        <v>127444600</v>
       </c>
       <c r="B25" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3206,13 +3211,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>478071</v>
+        <v>478030</v>
       </c>
       <c r="R25" t="n">
-        <v>6821124</v>
+        <v>6821197</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3241,7 +3246,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3251,7 +3256,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3271,17 +3276,17 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
+          <t>Peter Turander, Håkan Thenander, Bo karlstens, Birgitta Kvist, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127444600</v>
+        <v>127443315</v>
       </c>
       <c r="B26" t="n">
-        <v>57663</v>
+        <v>79029</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3289,42 +3294,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Harabacken, Harabacken, Dlr</t>
+          <t>Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>478030</v>
+        <v>478109</v>
       </c>
       <c r="R26" t="n">
-        <v>6821197</v>
+        <v>6820979</v>
       </c>
       <c r="S26" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3353,7 +3353,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3363,7 +3363,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3378,12 +3378,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3393,7 +3393,7 @@
         <v>127451855</v>
       </c>
       <c r="B27" t="n">
-        <v>79055</v>
+        <v>79061</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3499,7 +3499,7 @@
         <v>127445612</v>
       </c>
       <c r="B28" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3606,7 +3606,7 @@
         <v>127445678</v>
       </c>
       <c r="B29" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3715,10 +3715,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127443983</v>
+        <v>127441057</v>
       </c>
       <c r="B30" t="n">
-        <v>91341</v>
+        <v>57669</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3726,37 +3726,42 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Kuusikallio, Kuusikallio, Dlr</t>
+          <t>Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>478068</v>
+        <v>478319</v>
       </c>
       <c r="R30" t="n">
-        <v>6821169</v>
+        <v>6820790</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3785,7 +3790,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3795,7 +3800,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3810,22 +3815,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127445756</v>
+        <v>127443983</v>
       </c>
       <c r="B31" t="n">
-        <v>79023</v>
+        <v>91349</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3833,37 +3838,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Harabacken, Harabacken, Dlr</t>
+          <t>Kuusikallio, Kuusikallio, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>478104</v>
+        <v>478068</v>
       </c>
       <c r="R31" t="n">
-        <v>6821165</v>
+        <v>6821169</v>
       </c>
       <c r="S31" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3892,7 +3897,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3902,7 +3907,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3929,10 +3934,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127441057</v>
+        <v>127445756</v>
       </c>
       <c r="B32" t="n">
-        <v>57663</v>
+        <v>79029</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3940,42 +3945,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Harabacken, Dlr</t>
+          <t>Harabacken, Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>478319</v>
+        <v>478104</v>
       </c>
       <c r="R32" t="n">
-        <v>6820790</v>
+        <v>6821165</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4004,7 +4004,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4014,7 +4014,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4029,22 +4029,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127444491</v>
+        <v>127444793</v>
       </c>
       <c r="B33" t="n">
-        <v>79055</v>
+        <v>57832</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4052,37 +4052,42 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>185</v>
+        <v>103021</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Harabacken, Harabacken, Dlr</t>
+          <t>Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>478062</v>
+        <v>478245</v>
       </c>
       <c r="R33" t="n">
-        <v>6821201</v>
+        <v>6821068</v>
       </c>
       <c r="S33" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4111,7 +4116,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4121,12 +4126,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:07</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Sparsamt på gran</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4141,22 +4141,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127444374</v>
+        <v>127444491</v>
       </c>
       <c r="B34" t="n">
-        <v>79055</v>
+        <v>79061</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4188,13 +4188,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>478068</v>
+        <v>478062</v>
       </c>
       <c r="R34" t="n">
-        <v>6821169</v>
+        <v>6821201</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4233,7 +4233,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Sparsamt på gran</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4248,22 +4253,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127444793</v>
+        <v>127444374</v>
       </c>
       <c r="B35" t="n">
-        <v>57826</v>
+        <v>79061</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4271,39 +4276,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103021</v>
+        <v>185</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Harabacken, Dlr</t>
+          <t>Harabacken, Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>478245</v>
+        <v>478068</v>
       </c>
       <c r="R35" t="n">
-        <v>6821068</v>
+        <v>6821169</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4335,7 +4335,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4345,7 +4345,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4360,12 +4360,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -4375,7 +4375,7 @@
         <v>127444001</v>
       </c>
       <c r="B36" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4479,10 +4479,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127445635</v>
+        <v>127443762</v>
       </c>
       <c r="B37" t="n">
-        <v>79612</v>
+        <v>57672</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4490,34 +4490,39 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Harabacken, Dlr</t>
+          <t>Harabacken, Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>478265</v>
+        <v>478071</v>
       </c>
       <c r="R37" t="n">
-        <v>6821019</v>
+        <v>6821147</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4549,7 +4554,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4559,7 +4564,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4574,22 +4579,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127443762</v>
+        <v>127444502</v>
       </c>
       <c r="B38" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4626,13 +4631,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>478071</v>
+        <v>478062</v>
       </c>
       <c r="R38" t="n">
-        <v>6821147</v>
+        <v>6821201</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4661,7 +4666,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4671,7 +4676,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4686,22 +4691,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127444502</v>
+        <v>127445635</v>
       </c>
       <c r="B39" t="n">
-        <v>57666</v>
+        <v>79618</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4709,42 +4714,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Harabacken, Harabacken, Dlr</t>
+          <t>Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>478062</v>
+        <v>478265</v>
       </c>
       <c r="R39" t="n">
-        <v>6821201</v>
+        <v>6821019</v>
       </c>
       <c r="S39" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4773,7 +4773,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4783,7 +4783,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4798,12 +4798,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -4813,7 +4813,7 @@
         <v>127444767</v>
       </c>
       <c r="B40" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4920,7 +4920,7 @@
         <v>127443785</v>
       </c>
       <c r="B41" t="n">
-        <v>58036</v>
+        <v>58042</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5032,7 +5032,7 @@
         <v>127443466</v>
       </c>
       <c r="B42" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5139,7 +5139,7 @@
         <v>127444496</v>
       </c>
       <c r="B43" t="n">
-        <v>75147</v>
+        <v>75153</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5246,7 +5246,7 @@
         <v>127444690</v>
       </c>
       <c r="B44" t="n">
-        <v>57826</v>
+        <v>57832</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5355,10 +5355,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127445040</v>
+        <v>127444469</v>
       </c>
       <c r="B45" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5390,13 +5390,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>478072</v>
+        <v>478048</v>
       </c>
       <c r="R45" t="n">
-        <v>6821204</v>
+        <v>6821183</v>
       </c>
       <c r="S45" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5435,12 +5435,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:22</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>På tall</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5455,12 +5450,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -5470,7 +5465,7 @@
         <v>127443816</v>
       </c>
       <c r="B46" t="n">
-        <v>79055</v>
+        <v>79061</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5577,7 +5572,7 @@
         <v>127443715</v>
       </c>
       <c r="B47" t="n">
-        <v>79055</v>
+        <v>79061</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5681,10 +5676,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127444469</v>
+        <v>127445040</v>
       </c>
       <c r="B48" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5716,13 +5711,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>478048</v>
+        <v>478072</v>
       </c>
       <c r="R48" t="n">
-        <v>6821183</v>
+        <v>6821204</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5751,7 +5746,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5761,7 +5756,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5776,12 +5776,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Peter Turander, Håkan Thenander, Bo karlstens, Birgitta Kvist, Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -5791,7 +5791,7 @@
         <v>127443685</v>
       </c>
       <c r="B49" t="n">
-        <v>58036</v>
+        <v>58042</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5903,7 +5903,7 @@
         <v>127444902</v>
       </c>
       <c r="B50" t="n">
-        <v>79055</v>
+        <v>79061</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6015,7 +6015,7 @@
         <v>127443980</v>
       </c>
       <c r="B51" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6122,7 +6122,7 @@
         <v>127442782</v>
       </c>
       <c r="B52" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>

--- a/artfynd/A 33533-2025 artfynd.xlsx
+++ b/artfynd/A 33533-2025 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127443978</v>
+        <v>127445512</v>
       </c>
       <c r="B3" t="n">
-        <v>75153</v>
+        <v>79029</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,37 +798,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Harabacken, Dlr</t>
+          <t>Harabacken, Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>478207</v>
+        <v>478104</v>
       </c>
       <c r="R3" t="n">
-        <v>6821016</v>
+        <v>6821179</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,12 +867,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:20</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Vitgrynig nållav på äldre gran</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,22 +882,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens, Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127445652</v>
+        <v>127443978</v>
       </c>
       <c r="B4" t="n">
-        <v>79029</v>
+        <v>75153</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -910,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -934,13 +929,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>478270</v>
+        <v>478207</v>
       </c>
       <c r="R4" t="n">
-        <v>6821004</v>
+        <v>6821016</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -980,6 +975,11 @@
       <c r="AB4" t="inlineStr">
         <is>
           <t>10:20</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav på äldre gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1006,7 +1006,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127445512</v>
+        <v>127445652</v>
       </c>
       <c r="B5" t="n">
         <v>79029</v>
@@ -1037,17 +1037,17 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Harabacken, Harabacken, Dlr</t>
+          <t>Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>478104</v>
+        <v>478270</v>
       </c>
       <c r="R5" t="n">
-        <v>6821179</v>
+        <v>6821004</v>
       </c>
       <c r="S5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1101,12 +1101,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Bo karlstens, Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1658,10 +1658,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127444616</v>
+        <v>127447989</v>
       </c>
       <c r="B11" t="n">
-        <v>79061</v>
+        <v>79029</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1669,34 +1669,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Harabacken, Harabacken, Dlr</t>
+          <t>Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>478034</v>
+        <v>478360</v>
       </c>
       <c r="R11" t="n">
-        <v>6821199</v>
+        <v>6820946</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1753,22 +1753,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Peter Turander, Håkan Thenander, Bo karlstens, Birgitta Kvist, Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127447989</v>
+        <v>127444616</v>
       </c>
       <c r="B12" t="n">
-        <v>79029</v>
+        <v>79061</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1776,34 +1776,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Harabacken, Dlr</t>
+          <t>Harabacken, Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>478360</v>
+        <v>478034</v>
       </c>
       <c r="R12" t="n">
-        <v>6820946</v>
+        <v>6821199</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1860,44 +1860,44 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127443080</v>
+        <v>127444817</v>
       </c>
       <c r="B13" t="n">
-        <v>98384</v>
+        <v>79061</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219790</v>
+        <v>185</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1907,13 +1907,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>478309</v>
+        <v>478071</v>
       </c>
       <c r="R13" t="n">
-        <v>6820751</v>
+        <v>6821227</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1952,7 +1952,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1967,44 +1972,44 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Peter Turander, Håkan Thenander, Bo karlstens, Birgitta Kvist, Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127444817</v>
+        <v>127443080</v>
       </c>
       <c r="B14" t="n">
-        <v>79061</v>
+        <v>98385</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>185</v>
+        <v>219790</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2014,13 +2019,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>478071</v>
+        <v>478309</v>
       </c>
       <c r="R14" t="n">
-        <v>6821227</v>
+        <v>6820751</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2049,7 +2054,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2059,12 +2064,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:22</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>På gran</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2079,12 +2079,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Birgitta Kvist, Bengt Oldhammer, Bo karlstens</t>
+          <t>Bo karlstens, Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2410,7 +2410,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Peter Turander, Håkan Thenander, Bo karlstens, Birgitta Kvist, Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2517,7 +2517,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
+          <t>Peter Turander, Håkan Thenander, Bo karlstens, Birgitta Kvist, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2731,7 +2731,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Peter Turander, Håkan Thenander, Bo karlstens, Birgitta Kvist, Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2845,10 +2845,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127443809</v>
+        <v>127443690</v>
       </c>
       <c r="B22" t="n">
-        <v>79061</v>
+        <v>57669</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2856,37 +2856,42 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>185</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Harabacken, Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>478054</v>
+        <v>478071</v>
       </c>
       <c r="R22" t="n">
-        <v>6821168</v>
+        <v>6821124</v>
       </c>
       <c r="S22" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2915,7 +2920,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2925,7 +2930,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2940,22 +2945,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127444809</v>
+        <v>127444600</v>
       </c>
       <c r="B23" t="n">
-        <v>79029</v>
+        <v>57669</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2963,34 +2968,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Harabacken, Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>478062</v>
+        <v>478030</v>
       </c>
       <c r="R23" t="n">
-        <v>6821226</v>
+        <v>6821197</v>
       </c>
       <c r="S23" t="n">
         <v>9</v>
@@ -3022,7 +3032,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3032,7 +3042,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3047,22 +3057,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Bo karlstens, Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127443690</v>
+        <v>127443809</v>
       </c>
       <c r="B24" t="n">
-        <v>57669</v>
+        <v>79061</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3070,42 +3080,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>185</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Harabacken, Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>478071</v>
+        <v>478054</v>
       </c>
       <c r="R24" t="n">
-        <v>6821124</v>
+        <v>6821168</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3134,7 +3139,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3144,7 +3149,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3159,22 +3164,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127444600</v>
+        <v>127444809</v>
       </c>
       <c r="B25" t="n">
-        <v>57669</v>
+        <v>79029</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3182,39 +3187,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Harabacken, Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>478030</v>
+        <v>478062</v>
       </c>
       <c r="R25" t="n">
-        <v>6821197</v>
+        <v>6821226</v>
       </c>
       <c r="S25" t="n">
         <v>9</v>
@@ -3246,7 +3246,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3256,7 +3256,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3271,12 +3271,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Peter Turander, Håkan Thenander, Bo karlstens, Birgitta Kvist, Bengt Oldhammer</t>
+          <t>Bo karlstens, Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3496,10 +3496,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127445612</v>
+        <v>127445678</v>
       </c>
       <c r="B28" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3507,37 +3507,42 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Harabacken, Dlr</t>
+          <t>Kuusikallio, Kuusikallio, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>478265</v>
+        <v>478106</v>
       </c>
       <c r="R28" t="n">
-        <v>6821033</v>
+        <v>6821168</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3566,7 +3571,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3576,7 +3581,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3591,22 +3596,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127445678</v>
+        <v>127445612</v>
       </c>
       <c r="B29" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3614,42 +3619,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Kuusikallio, Kuusikallio, Dlr</t>
+          <t>Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>478106</v>
+        <v>478265</v>
       </c>
       <c r="R29" t="n">
-        <v>6821168</v>
+        <v>6821033</v>
       </c>
       <c r="S29" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3678,7 +3678,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3688,7 +3688,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3703,22 +3703,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127441057</v>
+        <v>127443983</v>
       </c>
       <c r="B30" t="n">
-        <v>57669</v>
+        <v>91350</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3726,42 +3726,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Harabacken, Dlr</t>
+          <t>Kuusikallio, Kuusikallio, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>478319</v>
+        <v>478068</v>
       </c>
       <c r="R30" t="n">
-        <v>6820790</v>
+        <v>6821169</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3790,7 +3785,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3800,7 +3795,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3815,22 +3810,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127443983</v>
+        <v>127441057</v>
       </c>
       <c r="B31" t="n">
-        <v>91349</v>
+        <v>57669</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3838,37 +3833,42 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Kuusikallio, Kuusikallio, Dlr</t>
+          <t>Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>478068</v>
+        <v>478319</v>
       </c>
       <c r="R31" t="n">
-        <v>6821169</v>
+        <v>6820790</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3897,7 +3897,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3907,7 +3907,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3922,12 +3922,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -4041,10 +4041,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127444793</v>
+        <v>127444491</v>
       </c>
       <c r="B33" t="n">
-        <v>57832</v>
+        <v>79061</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4052,42 +4052,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103021</v>
+        <v>185</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Harabacken, Dlr</t>
+          <t>Harabacken, Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>478245</v>
+        <v>478062</v>
       </c>
       <c r="R33" t="n">
-        <v>6821068</v>
+        <v>6821201</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4116,7 +4111,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4126,7 +4121,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Sparsamt på gran</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4141,19 +4141,19 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127444491</v>
+        <v>127444374</v>
       </c>
       <c r="B34" t="n">
         <v>79061</v>
@@ -4188,13 +4188,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>478062</v>
+        <v>478068</v>
       </c>
       <c r="R34" t="n">
-        <v>6821201</v>
+        <v>6821169</v>
       </c>
       <c r="S34" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4233,12 +4233,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:07</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Sparsamt på gran</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4253,22 +4248,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127444374</v>
+        <v>127444793</v>
       </c>
       <c r="B35" t="n">
-        <v>79061</v>
+        <v>57832</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4276,34 +4271,39 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>185</v>
+        <v>103021</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Harabacken, Harabacken, Dlr</t>
+          <t>Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>478068</v>
+        <v>478245</v>
       </c>
       <c r="R35" t="n">
-        <v>6821169</v>
+        <v>6821068</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4335,7 +4335,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4345,7 +4345,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4360,12 +4360,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -4584,7 +4584,7 @@
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
+          <t>Peter Turander, Håkan Thenander, Bo karlstens, Birgitta Kvist, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
@@ -4810,48 +4810,53 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127444767</v>
+        <v>127443785</v>
       </c>
       <c r="B40" t="n">
-        <v>79029</v>
+        <v>58042</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>478245</v>
+        <v>478207</v>
       </c>
       <c r="R40" t="n">
-        <v>6821068</v>
+        <v>6821016</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4917,53 +4922,48 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127443785</v>
+        <v>127444767</v>
       </c>
       <c r="B41" t="n">
-        <v>58042</v>
+        <v>79029</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>478207</v>
+        <v>478245</v>
       </c>
       <c r="R41" t="n">
-        <v>6821016</v>
+        <v>6821068</v>
       </c>
       <c r="S41" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5355,10 +5355,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127444469</v>
+        <v>127443816</v>
       </c>
       <c r="B45" t="n">
-        <v>79029</v>
+        <v>79061</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5366,21 +5366,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5390,10 +5390,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>478048</v>
+        <v>478071</v>
       </c>
       <c r="R45" t="n">
-        <v>6821183</v>
+        <v>6821147</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5455,14 +5455,14 @@
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
+          <t>Peter Turander, Håkan Thenander, Bo karlstens, Birgitta Kvist, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127443816</v>
+        <v>127443715</v>
       </c>
       <c r="B46" t="n">
         <v>79061</v>
@@ -5493,14 +5493,14 @@
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Harabacken, Harabacken, Dlr</t>
+          <t>Kuusikallio, Kuusikallio, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>478071</v>
+        <v>478069</v>
       </c>
       <c r="R46" t="n">
-        <v>6821147</v>
+        <v>6821132</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5532,7 +5532,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5542,7 +5542,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5569,10 +5569,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127443715</v>
+        <v>127444469</v>
       </c>
       <c r="B47" t="n">
-        <v>79061</v>
+        <v>79029</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5580,34 +5580,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Kuusikallio, Kuusikallio, Dlr</t>
+          <t>Harabacken, Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>478069</v>
+        <v>478048</v>
       </c>
       <c r="R47" t="n">
-        <v>6821132</v>
+        <v>6821183</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5639,7 +5639,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5649,7 +5649,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD47" t="b">

--- a/artfynd/A 33533-2025 artfynd.xlsx
+++ b/artfynd/A 33533-2025 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127445512</v>
+        <v>127443978</v>
       </c>
       <c r="B3" t="n">
-        <v>79029</v>
+        <v>75153</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,37 +798,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Harabacken, Harabacken, Dlr</t>
+          <t>Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>478104</v>
+        <v>478207</v>
       </c>
       <c r="R3" t="n">
-        <v>6821179</v>
+        <v>6821016</v>
       </c>
       <c r="S3" t="n">
-        <v>9</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,7 +867,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav på äldre gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -882,22 +887,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Bo karlstens, Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127443978</v>
+        <v>127445652</v>
       </c>
       <c r="B4" t="n">
-        <v>75153</v>
+        <v>79029</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -905,21 +910,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,13 +934,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>478207</v>
+        <v>478270</v>
       </c>
       <c r="R4" t="n">
-        <v>6821016</v>
+        <v>6821004</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -975,11 +980,6 @@
       <c r="AB4" t="inlineStr">
         <is>
           <t>10:20</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Vitgrynig nållav på äldre gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1006,7 +1006,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127445652</v>
+        <v>127445512</v>
       </c>
       <c r="B5" t="n">
         <v>79029</v>
@@ -1037,17 +1037,17 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Harabacken, Dlr</t>
+          <t>Harabacken, Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>478270</v>
+        <v>478104</v>
       </c>
       <c r="R5" t="n">
-        <v>6821004</v>
+        <v>6821179</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1101,22 +1101,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens, Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127445695</v>
+        <v>127442809</v>
       </c>
       <c r="B6" t="n">
-        <v>57669</v>
+        <v>79029</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1124,42 +1124,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Harabacken, Harabacken, Dlr</t>
+          <t>Kuusikallio, Kuusikallio, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>478104</v>
+        <v>478309</v>
       </c>
       <c r="R6" t="n">
-        <v>6821165</v>
+        <v>6820751</v>
       </c>
       <c r="S6" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1188,7 +1183,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1198,7 +1193,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1225,7 +1220,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127442809</v>
+        <v>127445814</v>
       </c>
       <c r="B7" t="n">
         <v>79029</v>
@@ -1256,17 +1251,17 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kuusikallio, Kuusikallio, Dlr</t>
+          <t>Harabacken, Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>478309</v>
+        <v>478096</v>
       </c>
       <c r="R7" t="n">
-        <v>6820751</v>
+        <v>6821144</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1295,7 +1290,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1305,7 +1300,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1332,7 +1327,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127445814</v>
+        <v>127444509</v>
       </c>
       <c r="B8" t="n">
         <v>79029</v>
@@ -1363,17 +1358,17 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Harabacken, Harabacken, Dlr</t>
+          <t>Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>478096</v>
+        <v>478229</v>
       </c>
       <c r="R8" t="n">
-        <v>6821144</v>
+        <v>6821051</v>
       </c>
       <c r="S8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1402,7 +1397,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1412,7 +1407,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1427,22 +1422,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127444509</v>
+        <v>127445695</v>
       </c>
       <c r="B9" t="n">
-        <v>79029</v>
+        <v>57669</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1450,37 +1445,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Harabacken, Dlr</t>
+          <t>Harabacken, Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>478229</v>
+        <v>478104</v>
       </c>
       <c r="R9" t="n">
-        <v>6821051</v>
+        <v>6821165</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1519,7 +1519,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1534,22 +1534,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127442751</v>
+        <v>127447989</v>
       </c>
       <c r="B10" t="n">
-        <v>57669</v>
+        <v>79029</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1557,39 +1557,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>478022</v>
+        <v>478360</v>
       </c>
       <c r="R10" t="n">
-        <v>6820902</v>
+        <v>6820946</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1658,10 +1653,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127447989</v>
+        <v>127444616</v>
       </c>
       <c r="B11" t="n">
-        <v>79029</v>
+        <v>79061</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1669,34 +1664,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Harabacken, Dlr</t>
+          <t>Harabacken, Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>478360</v>
+        <v>478034</v>
       </c>
       <c r="R11" t="n">
-        <v>6820946</v>
+        <v>6821199</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1728,7 +1723,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1738,7 +1733,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1753,22 +1748,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127444616</v>
+        <v>127442751</v>
       </c>
       <c r="B12" t="n">
-        <v>79061</v>
+        <v>57669</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1776,34 +1771,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>185</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Harabacken, Harabacken, Dlr</t>
+          <t>Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>478034</v>
+        <v>478022</v>
       </c>
       <c r="R12" t="n">
-        <v>6821199</v>
+        <v>6820902</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1860,12 +1860,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -2198,10 +2198,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127444563</v>
+        <v>127444510</v>
       </c>
       <c r="B16" t="n">
-        <v>79061</v>
+        <v>57672</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2209,34 +2209,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Harabacken, Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>478024</v>
+        <v>478030</v>
       </c>
       <c r="R16" t="n">
-        <v>6821213</v>
+        <v>6821195</v>
       </c>
       <c r="S16" t="n">
         <v>9</v>
@@ -2268,7 +2273,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2278,7 +2283,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2293,22 +2298,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Bo karlstens, Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127444510</v>
+        <v>127444563</v>
       </c>
       <c r="B17" t="n">
-        <v>57672</v>
+        <v>79061</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2316,39 +2321,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Harabacken, Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>478030</v>
+        <v>478024</v>
       </c>
       <c r="R17" t="n">
-        <v>6821195</v>
+        <v>6821213</v>
       </c>
       <c r="S17" t="n">
         <v>9</v>
@@ -2380,7 +2380,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2390,7 +2390,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2405,12 +2405,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
+          <t>Bo karlstens, Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2517,7 +2517,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Peter Turander, Håkan Thenander, Bo karlstens, Birgitta Kvist, Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2838,17 +2838,17 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Bo karlstens, Birgitta Kvist, Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127443690</v>
+        <v>127443809</v>
       </c>
       <c r="B22" t="n">
-        <v>57669</v>
+        <v>79061</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2856,42 +2856,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>185</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Harabacken, Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>478071</v>
+        <v>478054</v>
       </c>
       <c r="R22" t="n">
-        <v>6821124</v>
+        <v>6821168</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2920,7 +2915,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2930,7 +2925,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2945,19 +2940,19 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127444600</v>
+        <v>127443690</v>
       </c>
       <c r="B23" t="n">
         <v>57669</v>
@@ -2997,13 +2992,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>478030</v>
+        <v>478071</v>
       </c>
       <c r="R23" t="n">
-        <v>6821197</v>
+        <v>6821124</v>
       </c>
       <c r="S23" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3032,7 +3027,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3042,7 +3037,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3069,10 +3064,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127443809</v>
+        <v>127444600</v>
       </c>
       <c r="B24" t="n">
-        <v>79061</v>
+        <v>57669</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3080,37 +3075,42 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>185</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Harabacken, Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>478054</v>
+        <v>478030</v>
       </c>
       <c r="R24" t="n">
-        <v>6821168</v>
+        <v>6821197</v>
       </c>
       <c r="S24" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3139,7 +3139,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3149,7 +3149,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3164,12 +3164,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -3390,10 +3390,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127451855</v>
+        <v>127445612</v>
       </c>
       <c r="B27" t="n">
-        <v>79061</v>
+        <v>79029</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3401,40 +3401,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>478077</v>
+        <v>478265</v>
       </c>
       <c r="R27" t="n">
-        <v>6820974</v>
+        <v>6821033</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3461,14 +3458,19 @@
           <t>2025-08-13</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-08-13</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>På gran</t>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3477,29 +3479,28 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127445678</v>
+        <v>127451855</v>
       </c>
       <c r="B28" t="n">
-        <v>57672</v>
+        <v>79061</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3507,42 +3508,40 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Kuusikallio, Kuusikallio, Dlr</t>
+          <t>Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>478106</v>
+        <v>478077</v>
       </c>
       <c r="R28" t="n">
-        <v>6821168</v>
+        <v>6820974</v>
       </c>
       <c r="S28" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3569,19 +3568,14 @@
           <t>2025-08-13</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>12:47</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-08-13</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>12:47</t>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3590,28 +3584,29 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127445612</v>
+        <v>127445678</v>
       </c>
       <c r="B29" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3619,37 +3614,42 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Harabacken, Dlr</t>
+          <t>Kuusikallio, Kuusikallio, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>478265</v>
+        <v>478106</v>
       </c>
       <c r="R29" t="n">
-        <v>6821033</v>
+        <v>6821168</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3678,7 +3678,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3688,7 +3688,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3703,12 +3703,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -3822,10 +3822,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127441057</v>
+        <v>127445756</v>
       </c>
       <c r="B31" t="n">
-        <v>57669</v>
+        <v>79029</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3833,42 +3833,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Harabacken, Dlr</t>
+          <t>Harabacken, Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>478319</v>
+        <v>478104</v>
       </c>
       <c r="R31" t="n">
-        <v>6820790</v>
+        <v>6821165</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3897,7 +3892,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3907,7 +3902,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3922,22 +3917,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127445756</v>
+        <v>127441057</v>
       </c>
       <c r="B32" t="n">
-        <v>79029</v>
+        <v>57669</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3945,37 +3940,42 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Harabacken, Harabacken, Dlr</t>
+          <t>Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>478104</v>
+        <v>478319</v>
       </c>
       <c r="R32" t="n">
-        <v>6821165</v>
+        <v>6820790</v>
       </c>
       <c r="S32" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4004,7 +4004,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4014,7 +4014,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4029,12 +4029,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -4479,7 +4479,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127443762</v>
+        <v>127444502</v>
       </c>
       <c r="B37" t="n">
         <v>57672</v>
@@ -4519,13 +4519,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>478071</v>
+        <v>478062</v>
       </c>
       <c r="R37" t="n">
-        <v>6821147</v>
+        <v>6821201</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4554,7 +4554,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4564,7 +4564,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4579,19 +4579,19 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Peter Turander, Håkan Thenander, Bo karlstens, Birgitta Kvist, Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127444502</v>
+        <v>127443762</v>
       </c>
       <c r="B38" t="n">
         <v>57672</v>
@@ -4631,13 +4631,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>478062</v>
+        <v>478071</v>
       </c>
       <c r="R38" t="n">
-        <v>6821201</v>
+        <v>6821147</v>
       </c>
       <c r="S38" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4666,7 +4666,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4676,7 +4676,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4691,12 +4691,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -5029,10 +5029,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127443466</v>
+        <v>127444496</v>
       </c>
       <c r="B42" t="n">
-        <v>79029</v>
+        <v>75153</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5040,21 +5040,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5064,10 +5064,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>478105</v>
+        <v>478229</v>
       </c>
       <c r="R42" t="n">
-        <v>6820956</v>
+        <v>6821051</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5136,10 +5136,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127444496</v>
+        <v>127443466</v>
       </c>
       <c r="B43" t="n">
-        <v>75153</v>
+        <v>79029</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5147,21 +5147,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5171,10 +5171,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>478229</v>
+        <v>478105</v>
       </c>
       <c r="R43" t="n">
-        <v>6821051</v>
+        <v>6820956</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5455,7 +5455,7 @@
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Peter Turander, Håkan Thenander, Bo karlstens, Birgitta Kvist, Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -5569,7 +5569,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127444469</v>
+        <v>127445040</v>
       </c>
       <c r="B47" t="n">
         <v>79029</v>
@@ -5604,13 +5604,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>478048</v>
+        <v>478072</v>
       </c>
       <c r="R47" t="n">
-        <v>6821183</v>
+        <v>6821204</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5639,7 +5639,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5649,7 +5649,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5664,19 +5669,19 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127445040</v>
+        <v>127444469</v>
       </c>
       <c r="B48" t="n">
         <v>79029</v>
@@ -5711,13 +5716,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>478072</v>
+        <v>478048</v>
       </c>
       <c r="R48" t="n">
-        <v>6821204</v>
+        <v>6821183</v>
       </c>
       <c r="S48" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5746,7 +5751,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5756,12 +5761,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:22</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>På tall</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5776,12 +5776,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Bo karlstens, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -5900,10 +5900,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127444902</v>
+        <v>127443980</v>
       </c>
       <c r="B50" t="n">
-        <v>79061</v>
+        <v>79029</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5911,37 +5911,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Harabacken, Harabacken, Dlr</t>
+          <t>Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>478072</v>
+        <v>478207</v>
       </c>
       <c r="R50" t="n">
-        <v>6821204</v>
+        <v>6821016</v>
       </c>
       <c r="S50" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5970,7 +5970,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5980,12 +5980,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:22</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>På gran</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6000,22 +5995,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127443980</v>
+        <v>127444902</v>
       </c>
       <c r="B51" t="n">
-        <v>79029</v>
+        <v>79061</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6023,37 +6018,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Harabacken, Dlr</t>
+          <t>Harabacken, Harabacken, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>478207</v>
+        <v>478072</v>
       </c>
       <c r="R51" t="n">
-        <v>6821016</v>
+        <v>6821204</v>
       </c>
       <c r="S51" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6082,7 +6077,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6092,7 +6087,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6107,12 +6107,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
